--- a/Data Files/TestData.xlsx
+++ b/Data Files/TestData.xlsx
@@ -1,63 +1,64 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23801"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CodeCompare\Rohini\AccessWeb\Data Files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gitRemoteViz\AccessWeb\Data Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6196BAA-3EAA-4EDA-AD57-9E2749D750F7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D4CF4BE-3382-4862-B4C1-45A7850B092C}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10560" tabRatio="954" firstSheet="7" activeTab="15" xr2:uid="{C6F85985-84AE-4DCB-8550-9B2F16782E4E}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10560" tabRatio="954" activeTab="1" xr2:uid="{C6F85985-84AE-4DCB-8550-9B2F16782E4E}"/>
   </bookViews>
   <sheets>
     <sheet name="Index" sheetId="26" r:id="rId1"/>
-    <sheet name="Audit Logs" sheetId="47" r:id="rId2"/>
-    <sheet name="ChangePasswd" sheetId="46" r:id="rId3"/>
-    <sheet name="AppComposerNew" sheetId="44" r:id="rId4"/>
-    <sheet name="AppComposer" sheetId="45" r:id="rId5"/>
-    <sheet name="FilesTableCols " sheetId="43" r:id="rId6"/>
-    <sheet name="FileViewer2020.4" sheetId="41" r:id="rId7"/>
-    <sheet name="ManageBookMark" sheetId="40" r:id="rId8"/>
-    <sheet name="2020.4" sheetId="39" r:id="rId9"/>
-    <sheet name="FileViewerJobs" sheetId="37" r:id="rId10"/>
-    <sheet name="Generic_Actions" sheetId="36" r:id="rId11"/>
-    <sheet name="Access_Management" sheetId="32" r:id="rId12"/>
-    <sheet name="Preferences" sheetId="33" r:id="rId13"/>
-    <sheet name="JobsTableCols" sheetId="29" r:id="rId14"/>
-    <sheet name="Cluster_Registration" sheetId="28" r:id="rId15"/>
-    <sheet name="JobDetails" sheetId="30" r:id="rId16"/>
-    <sheet name="JobMonitoringGeneric" sheetId="27" r:id="rId17"/>
-    <sheet name="ViewDetailsForNonOwner" sheetId="23" r:id="rId18"/>
-    <sheet name="ProfileSubmissions" sheetId="21" r:id="rId19"/>
-    <sheet name="ProfileOperations" sheetId="14" r:id="rId20"/>
-    <sheet name="JobAction" sheetId="5" r:id="rId21"/>
-    <sheet name="JobArrayAction" sheetId="31" r:id="rId22"/>
-    <sheet name="JobActionNotJobOwner" sheetId="20" r:id="rId23"/>
-    <sheet name="JobActionIcon" sheetId="18" r:id="rId24"/>
-    <sheet name="JobActionIconNotJobOwner" sheetId="24" r:id="rId25"/>
-    <sheet name="JS-Latest" sheetId="16" r:id="rId26"/>
-    <sheet name="BookMarks" sheetId="17" r:id="rId27"/>
-    <sheet name="JobSubmission-Folder operations" sheetId="12" r:id="rId28"/>
-    <sheet name="FolderOperations" sheetId="11" r:id="rId29"/>
-    <sheet name="JobSubmission-File operations" sheetId="13" r:id="rId30"/>
-    <sheet name="FileTab_GenericTC" sheetId="42" r:id="rId31"/>
-    <sheet name="FileOperations" sheetId="9" r:id="rId32"/>
-    <sheet name="LoginData" sheetId="1" r:id="rId33"/>
-    <sheet name="JobFilters" sheetId="8" r:id="rId34"/>
-    <sheet name="FileViewerOps" sheetId="15" r:id="rId35"/>
-    <sheet name="CreateFolder" sheetId="2" r:id="rId36"/>
-    <sheet name="CreateFile" sheetId="3" r:id="rId37"/>
-    <sheet name="CompletedJobsFolder" sheetId="7" r:id="rId38"/>
-    <sheet name="RunningFolder" sheetId="6" r:id="rId39"/>
-    <sheet name="JobFiltersSavedFilters" sheetId="19" r:id="rId40"/>
+    <sheet name="MultiFileFolderOps" sheetId="48" r:id="rId2"/>
+    <sheet name="Audit Logs" sheetId="47" r:id="rId3"/>
+    <sheet name="ChangePasswd" sheetId="46" r:id="rId4"/>
+    <sheet name="AppComposerNew" sheetId="44" r:id="rId5"/>
+    <sheet name="AppComposer" sheetId="45" r:id="rId6"/>
+    <sheet name="FilesTableCols " sheetId="43" r:id="rId7"/>
+    <sheet name="FileViewer2020.4" sheetId="41" r:id="rId8"/>
+    <sheet name="ManageBookMark" sheetId="40" r:id="rId9"/>
+    <sheet name="2020.4" sheetId="39" r:id="rId10"/>
+    <sheet name="FileViewerJobs" sheetId="37" r:id="rId11"/>
+    <sheet name="Generic_Actions" sheetId="36" r:id="rId12"/>
+    <sheet name="Access_Management" sheetId="32" r:id="rId13"/>
+    <sheet name="Preferences" sheetId="33" r:id="rId14"/>
+    <sheet name="JobsTableCols" sheetId="29" r:id="rId15"/>
+    <sheet name="Cluster_Registration" sheetId="28" r:id="rId16"/>
+    <sheet name="JobDetails" sheetId="30" r:id="rId17"/>
+    <sheet name="JobMonitoringGeneric" sheetId="27" r:id="rId18"/>
+    <sheet name="ViewDetailsForNonOwner" sheetId="23" r:id="rId19"/>
+    <sheet name="ProfileSubmissions" sheetId="21" r:id="rId20"/>
+    <sheet name="ProfileOperations" sheetId="14" r:id="rId21"/>
+    <sheet name="JobAction" sheetId="5" r:id="rId22"/>
+    <sheet name="JobArrayAction" sheetId="31" r:id="rId23"/>
+    <sheet name="JobActionNotJobOwner" sheetId="20" r:id="rId24"/>
+    <sheet name="JobActionIcon" sheetId="18" r:id="rId25"/>
+    <sheet name="JobActionIconNotJobOwner" sheetId="24" r:id="rId26"/>
+    <sheet name="JS-Latest" sheetId="16" r:id="rId27"/>
+    <sheet name="BookMarks" sheetId="17" r:id="rId28"/>
+    <sheet name="JobSubmission-Folder operations" sheetId="12" r:id="rId29"/>
+    <sheet name="FolderOperations" sheetId="11" r:id="rId30"/>
+    <sheet name="JobSubmission-File operations" sheetId="13" r:id="rId31"/>
+    <sheet name="FileTab_GenericTC" sheetId="42" r:id="rId32"/>
+    <sheet name="FileOperations" sheetId="9" r:id="rId33"/>
+    <sheet name="LoginData" sheetId="1" r:id="rId34"/>
+    <sheet name="JobFilters" sheetId="8" r:id="rId35"/>
+    <sheet name="FileViewerOps" sheetId="15" r:id="rId36"/>
+    <sheet name="CreateFolder" sheetId="2" r:id="rId37"/>
+    <sheet name="CreateFile" sheetId="3" r:id="rId38"/>
+    <sheet name="CompletedJobsFolder" sheetId="7" r:id="rId39"/>
+    <sheet name="RunningFolder" sheetId="6" r:id="rId40"/>
+    <sheet name="JobFiltersSavedFilters" sheetId="19" r:id="rId41"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="25" hidden="1">'JS-Latest'!$A$1:$G$56</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">ProfileOperations!$A$1:$G$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">ProfileSubmissions!$A$1:$G$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="26" hidden="1">'JS-Latest'!$A$1:$G$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">ProfileOperations!$A$1:$G$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">ProfileSubmissions!$A$1:$G$37</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -77,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3309" uniqueCount="1106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3494" uniqueCount="1147">
   <si>
     <t>username</t>
   </si>
@@ -3397,6 +3398,129 @@
   </si>
   <si>
     <t>Test case to edit file in job details page Input Folder</t>
+  </si>
+  <si>
+    <t>FilesIcon</t>
+  </si>
+  <si>
+    <t>Both</t>
+  </si>
+  <si>
+    <t>Test case to make sure the output files and folders are displayed under output section and the user is able to delete by selecting the multiple files and folders</t>
+  </si>
+  <si>
+    <t>Test case to make sure the output files and folders are displayed under output section and the user is able to create new file by selecting the multiple files and folders</t>
+  </si>
+  <si>
+    <t>Test case to make sure the output files and folders are displayed under output section and the user is able to download by selecting the multiple files and folders</t>
+  </si>
+  <si>
+    <t>BothIcon</t>
+  </si>
+  <si>
+    <t>Test case to make sure the output files and folders are displayed under output section and the user is able to delete by selecting the multiple files and folders using top menu icon</t>
+  </si>
+  <si>
+    <t>Test case to make sure the output files and folders are displayed under output section and the user is able to resubmit by selecting the multiple files and folders using top menu icon</t>
+  </si>
+  <si>
+    <t>Test case to make sure the output files and folders are displayed under output section and the user is able to download by selecting the multiple files and folders using top menu icon</t>
+  </si>
+  <si>
+    <t>Test case to make sure the output files are displayed under output section and the user is able to delete by selecting the multiple Files</t>
+  </si>
+  <si>
+    <t>Test case to make sure the output files are displayed under output section and the user is able to create new file by selecting the multiple Files</t>
+  </si>
+  <si>
+    <t>Test case to make sure the output files are displayed under output section and the user is able to download by selecting the multiple Files</t>
+  </si>
+  <si>
+    <t>Test case to make sure the output files are displayed under output section and the user is able to delete by selecting the multiple Files using top menu icon</t>
+  </si>
+  <si>
+    <t>Test case to make sure the output files are displayed under output section and the user is able to resubmit by selecting the multiple Files using top menu icon</t>
+  </si>
+  <si>
+    <t>Test case to make sure the output files are displayed under output section and the user is able to download by selecting the multiple Files using top menu icon</t>
+  </si>
+  <si>
+    <t>Folders</t>
+  </si>
+  <si>
+    <t>Test case to make sure the output files are displayed under output section and the user is able to delete by selecting the multiple folders</t>
+  </si>
+  <si>
+    <t>Test case to make sure the output files are displayed under output section and the user is able to create new file by selecting the multiple folders</t>
+  </si>
+  <si>
+    <t>Test case to make sure the output files are displayed under output section and the user is able to download by selecting the multiple folders</t>
+  </si>
+  <si>
+    <t>FoldersIcon</t>
+  </si>
+  <si>
+    <t>Test case to make sure the output files are displayed under output section and the user is able to delete by selecting the multiple folders using top menu icon</t>
+  </si>
+  <si>
+    <t>Test case to make sure the output files are displayed under output section and the user is able to resubmit by selecting the multiple folders using top menu icon</t>
+  </si>
+  <si>
+    <t>Test case to make sure the output files are displayed under output section and the user is able to download by selecting the multiple folders using top menu icon</t>
+  </si>
+  <si>
+    <t>Test case to make sure the Input files are displayed under Input section and the user is able to download by selecting the multiple folders using top menu icon</t>
+  </si>
+  <si>
+    <t>Test case to make sure the Input files are displayed under Input section and the user is able to resubmit by selecting the multiple folders using top menu icon</t>
+  </si>
+  <si>
+    <t>Test case to make sure the Input files are displayed under Input section and the user is able to delete by selecting the multiple folders using top menu icon</t>
+  </si>
+  <si>
+    <t>Test case to make sure the Input files are displayed under Input section and the user is able to download by selecting the multiple folders</t>
+  </si>
+  <si>
+    <t>Test case to make sure the Input files are displayed under Input section and the user is able to create new file by selecting the multiple folders</t>
+  </si>
+  <si>
+    <t>Test case to make sure the Input files are displayed under Input section and the user is able to delete by selecting the multiple folders</t>
+  </si>
+  <si>
+    <t>Test case to make sure the Input files are displayed under Input section and the user is able to download by selecting the multiple Files using top menu icon</t>
+  </si>
+  <si>
+    <t>Test case to make sure the Input files are displayed under Input section and the user is able to resubmit by selecting the multiple Files using top menu icon</t>
+  </si>
+  <si>
+    <t>Test case to make sure the Input files are displayed under Input section and the user is able to delete by selecting the multiple Files using top menu icon</t>
+  </si>
+  <si>
+    <t>Test case to make sure the Input files are displayed under Input section and the user is able to download by selecting the multiple Files</t>
+  </si>
+  <si>
+    <t>Test case to make sure the Input files are displayed under Input section and the user is able to create new file by selecting the multiple Files</t>
+  </si>
+  <si>
+    <t>Test case to make sure the Input files are displayed under Input section and the user is able to delete by selecting the multiple Files</t>
+  </si>
+  <si>
+    <t>Test case to make sure the Input files and folders are displayed under Input section and the user is able to download by selecting the multiple files and folders using top menu icon</t>
+  </si>
+  <si>
+    <t>Test case to make sure the Input files and folders are displayed under Input section and the user is able to resubmit by selecting the multiple files and folders using top menu icon</t>
+  </si>
+  <si>
+    <t>Test case to make sure the Input files and folders are displayed under Input section and the user is able to delete by selecting the multiple files and folders using top menu icon</t>
+  </si>
+  <si>
+    <t>Test case to make sure the Input files and folders are displayed under Input section and the user is able to download by selecting the multiple files and folders</t>
+  </si>
+  <si>
+    <t>Test case to make sure the Input files and folders are displayed under Input section and the user is able to create new file by selecting the multiple files and folders</t>
+  </si>
+  <si>
+    <t>Test case to make sure the Input files and folders are displayed under Input section and the user is able to delete by selecting the multiple files and folders</t>
   </si>
 </sst>
 </file>
@@ -3454,7 +3578,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3475,6 +3599,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3523,7 +3653,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -3557,6 +3687,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Accent5" xfId="1" builtinId="45"/>
@@ -4109,6 +4240,54 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F523F3BF-8164-44E1-977A-66026445142F}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="38.6328125" customWidth="1"/>
+    <col min="2" max="2" width="11.08984375" customWidth="1"/>
+    <col min="3" max="3" width="10.90625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" t="s">
+        <v>273</v>
+      </c>
+      <c r="C1" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>767</v>
+      </c>
+      <c r="B2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>770</v>
+      </c>
+      <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" t="s">
+        <v>769</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4567093D-A8D5-4E03-9534-579CE219E49C}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -4448,7 +4627,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4B5724D-5463-4FCF-A4F1-F5DFAB6E3F70}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -4505,7 +4684,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55DC2C27-8A96-4A23-BB21-23846DE78349}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -4798,7 +4977,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{484BDA10-16FC-473B-B01F-8455443B2C0A}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -4970,7 +5149,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CE8C224-BA72-4C4C-B7BF-5463A9EB02C3}">
   <dimension ref="A1:F25"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -5491,7 +5670,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D482266D-B90F-4B77-ADCD-DBA0EB5AE431}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -5976,7 +6155,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B160D41-22A7-4DDD-97BB-D99E5654BA01}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -6374,7 +6553,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{414B5370-5029-483B-916B-4E563C4D6F93}">
   <dimension ref="A1:C15"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -6557,7 +6736,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07DE01A5-2C8B-4355-8451-CE73E53961BB}">
   <sheetPr codeName="Sheet2">
     <tabColor rgb="FF92D050"/>
@@ -6800,7 +6979,653 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C2E8DB6-985C-4A4D-B54D-754B4AB198CD}">
+  <dimension ref="A1:E37"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="146.90625" customWidth="1"/>
+    <col min="2" max="2" width="13.08984375" customWidth="1"/>
+    <col min="3" max="3" width="17.6328125" customWidth="1"/>
+    <col min="4" max="4" width="9.81640625" customWidth="1"/>
+    <col min="5" max="5" width="10.453125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" t="s">
+        <v>353</v>
+      </c>
+      <c r="D1" t="s">
+        <v>273</v>
+      </c>
+      <c r="E1" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>1128</v>
+      </c>
+      <c r="B2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" t="s">
+        <v>310</v>
+      </c>
+      <c r="D2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" t="s">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>1127</v>
+      </c>
+      <c r="B3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3" t="s">
+        <v>310</v>
+      </c>
+      <c r="D3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" t="s">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>1126</v>
+      </c>
+      <c r="B4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" t="s">
+        <v>310</v>
+      </c>
+      <c r="D4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" t="s">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>1124</v>
+      </c>
+      <c r="B5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" t="s">
+        <v>310</v>
+      </c>
+      <c r="D5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" t="s">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>1123</v>
+      </c>
+      <c r="B6" t="s">
+        <v>467</v>
+      </c>
+      <c r="C6" t="s">
+        <v>310</v>
+      </c>
+      <c r="D6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" t="s">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>1122</v>
+      </c>
+      <c r="B7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" t="s">
+        <v>310</v>
+      </c>
+      <c r="D7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" t="s">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>1120</v>
+      </c>
+      <c r="B8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" t="s">
+        <v>310</v>
+      </c>
+      <c r="D8" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" t="s">
+        <v>1106</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" t="s">
+        <v>310</v>
+      </c>
+      <c r="D9" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" t="s">
+        <v>1106</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>1118</v>
+      </c>
+      <c r="B10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" t="s">
+        <v>310</v>
+      </c>
+      <c r="D10" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" t="s">
+        <v>1106</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>1117</v>
+      </c>
+      <c r="B11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" t="s">
+        <v>310</v>
+      </c>
+      <c r="D11" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>1116</v>
+      </c>
+      <c r="B12" t="s">
+        <v>467</v>
+      </c>
+      <c r="C12" t="s">
+        <v>310</v>
+      </c>
+      <c r="D12" t="s">
+        <v>26</v>
+      </c>
+      <c r="E12" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>1115</v>
+      </c>
+      <c r="B13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" t="s">
+        <v>310</v>
+      </c>
+      <c r="D13" t="s">
+        <v>26</v>
+      </c>
+      <c r="E13" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>1114</v>
+      </c>
+      <c r="B14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" t="s">
+        <v>310</v>
+      </c>
+      <c r="D14" t="s">
+        <v>26</v>
+      </c>
+      <c r="E14" t="s">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B15" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" t="s">
+        <v>310</v>
+      </c>
+      <c r="D15" t="s">
+        <v>26</v>
+      </c>
+      <c r="E15" t="s">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B16" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" t="s">
+        <v>310</v>
+      </c>
+      <c r="D16" t="s">
+        <v>26</v>
+      </c>
+      <c r="E16" t="s">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>1110</v>
+      </c>
+      <c r="B17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" t="s">
+        <v>310</v>
+      </c>
+      <c r="D17" t="s">
+        <v>26</v>
+      </c>
+      <c r="E17" t="s">
+        <v>1107</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>1109</v>
+      </c>
+      <c r="B18" t="s">
+        <v>467</v>
+      </c>
+      <c r="C18" t="s">
+        <v>310</v>
+      </c>
+      <c r="D18" t="s">
+        <v>26</v>
+      </c>
+      <c r="E18" t="s">
+        <v>1107</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>1108</v>
+      </c>
+      <c r="B19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" t="s">
+        <v>310</v>
+      </c>
+      <c r="D19" t="s">
+        <v>26</v>
+      </c>
+      <c r="E19" t="s">
+        <v>1107</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20" s="25" t="s">
+        <v>1129</v>
+      </c>
+      <c r="B20" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="25" t="s">
+        <v>304</v>
+      </c>
+      <c r="D20" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="E20" s="25" t="s">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21" s="25" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B21" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="C21" s="25" t="s">
+        <v>304</v>
+      </c>
+      <c r="D21" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="E21" s="25" t="s">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A22" s="25" t="s">
+        <v>1131</v>
+      </c>
+      <c r="B22" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" s="25" t="s">
+        <v>304</v>
+      </c>
+      <c r="D22" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="E22" s="25" t="s">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A23" s="25" t="s">
+        <v>1132</v>
+      </c>
+      <c r="B23" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" s="25" t="s">
+        <v>304</v>
+      </c>
+      <c r="D23" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="E23" s="25" t="s">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A24" s="25" t="s">
+        <v>1133</v>
+      </c>
+      <c r="B24" s="25" t="s">
+        <v>467</v>
+      </c>
+      <c r="C24" s="25" t="s">
+        <v>304</v>
+      </c>
+      <c r="D24" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="E24" s="25" t="s">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A25" s="25" t="s">
+        <v>1134</v>
+      </c>
+      <c r="B25" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="C25" s="25" t="s">
+        <v>304</v>
+      </c>
+      <c r="D25" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="E25" s="25" t="s">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>1135</v>
+      </c>
+      <c r="B26" t="s">
+        <v>30</v>
+      </c>
+      <c r="C26" t="s">
+        <v>304</v>
+      </c>
+      <c r="D26" t="s">
+        <v>26</v>
+      </c>
+      <c r="E26" t="s">
+        <v>1106</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>1136</v>
+      </c>
+      <c r="B27" t="s">
+        <v>29</v>
+      </c>
+      <c r="C27" t="s">
+        <v>304</v>
+      </c>
+      <c r="D27" t="s">
+        <v>26</v>
+      </c>
+      <c r="E27" t="s">
+        <v>1106</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B28" t="s">
+        <v>27</v>
+      </c>
+      <c r="C28" t="s">
+        <v>304</v>
+      </c>
+      <c r="D28" t="s">
+        <v>26</v>
+      </c>
+      <c r="E28" t="s">
+        <v>1106</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>1138</v>
+      </c>
+      <c r="B29" t="s">
+        <v>30</v>
+      </c>
+      <c r="C29" t="s">
+        <v>304</v>
+      </c>
+      <c r="D29" t="s">
+        <v>26</v>
+      </c>
+      <c r="E29" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>1139</v>
+      </c>
+      <c r="B30" t="s">
+        <v>467</v>
+      </c>
+      <c r="C30" t="s">
+        <v>304</v>
+      </c>
+      <c r="D30" t="s">
+        <v>26</v>
+      </c>
+      <c r="E30" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>1140</v>
+      </c>
+      <c r="B31" t="s">
+        <v>27</v>
+      </c>
+      <c r="C31" t="s">
+        <v>304</v>
+      </c>
+      <c r="D31" t="s">
+        <v>26</v>
+      </c>
+      <c r="E31" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B32" t="s">
+        <v>30</v>
+      </c>
+      <c r="C32" t="s">
+        <v>304</v>
+      </c>
+      <c r="D32" t="s">
+        <v>26</v>
+      </c>
+      <c r="E32" t="s">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>1142</v>
+      </c>
+      <c r="B33" t="s">
+        <v>29</v>
+      </c>
+      <c r="C33" t="s">
+        <v>304</v>
+      </c>
+      <c r="D33" t="s">
+        <v>26</v>
+      </c>
+      <c r="E33" t="s">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B34" t="s">
+        <v>27</v>
+      </c>
+      <c r="C34" t="s">
+        <v>304</v>
+      </c>
+      <c r="D34" t="s">
+        <v>26</v>
+      </c>
+      <c r="E34" t="s">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B35" t="s">
+        <v>30</v>
+      </c>
+      <c r="C35" t="s">
+        <v>304</v>
+      </c>
+      <c r="D35" t="s">
+        <v>26</v>
+      </c>
+      <c r="E35" t="s">
+        <v>1107</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>1145</v>
+      </c>
+      <c r="B36" t="s">
+        <v>467</v>
+      </c>
+      <c r="C36" t="s">
+        <v>304</v>
+      </c>
+      <c r="D36" t="s">
+        <v>26</v>
+      </c>
+      <c r="E36" t="s">
+        <v>1107</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>1146</v>
+      </c>
+      <c r="B37" t="s">
+        <v>27</v>
+      </c>
+      <c r="C37" t="s">
+        <v>304</v>
+      </c>
+      <c r="D37" t="s">
+        <v>26</v>
+      </c>
+      <c r="E37" t="s">
+        <v>1107</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4692B37E-0216-4972-A110-E1B81B06E6C4}">
   <sheetPr codeName="Sheet3">
     <tabColor rgb="FF92D050"/>
@@ -8012,182 +8837,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB0C9BC5-E2CE-4417-A398-52D4FBA952C1}">
-  <dimension ref="A1:M11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="10.90625" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" customWidth="1"/>
-    <col min="13" max="13" width="86.6328125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>353</v>
-      </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
-        <v>302</v>
-      </c>
-      <c r="D1" t="s">
-        <v>65</v>
-      </c>
-      <c r="E1" t="s">
-        <v>147</v>
-      </c>
-      <c r="F1" t="s">
-        <v>187</v>
-      </c>
-      <c r="G1" t="s">
-        <v>179</v>
-      </c>
-      <c r="H1" t="s">
-        <v>180</v>
-      </c>
-      <c r="I1" t="s">
-        <v>1057</v>
-      </c>
-      <c r="J1" t="s">
-        <v>89</v>
-      </c>
-      <c r="K1" t="s">
-        <v>273</v>
-      </c>
-      <c r="L1" t="s">
-        <v>1058</v>
-      </c>
-      <c r="M1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>1059</v>
-      </c>
-      <c r="M2" t="s">
-        <v>1060</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>1061</v>
-      </c>
-      <c r="B3" t="s">
-        <v>540</v>
-      </c>
-      <c r="M3" t="s">
-        <v>1062</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>1063</v>
-      </c>
-      <c r="M4" t="s">
-        <v>1064</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>1065</v>
-      </c>
-      <c r="M5" t="s">
-        <v>1066</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>1067</v>
-      </c>
-      <c r="M6" t="s">
-        <v>1068</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>1069</v>
-      </c>
-      <c r="M7" t="s">
-        <v>1070</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>1071</v>
-      </c>
-      <c r="B8" t="s">
-        <v>326</v>
-      </c>
-      <c r="M8" t="s">
-        <v>1072</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>1073</v>
-      </c>
-      <c r="M9" t="s">
-        <v>1074</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>1075</v>
-      </c>
-      <c r="B10" t="s">
-        <v>326</v>
-      </c>
-      <c r="M10" t="s">
-        <v>1076</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>49</v>
-      </c>
-      <c r="C11" t="s">
-        <v>12</v>
-      </c>
-      <c r="D11" t="s">
-        <v>30</v>
-      </c>
-      <c r="E11" t="s">
-        <v>15</v>
-      </c>
-      <c r="F11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G11" t="s">
-        <v>181</v>
-      </c>
-      <c r="H11">
-        <v>2</v>
-      </c>
-      <c r="I11" t="s">
-        <v>208</v>
-      </c>
-      <c r="J11" t="s">
-        <v>91</v>
-      </c>
-      <c r="K11" t="s">
-        <v>26</v>
-      </c>
-      <c r="L11" t="s">
-        <v>100</v>
-      </c>
-      <c r="M11" t="s">
-        <v>1077</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED88715B-2C1F-4B02-9C56-197D358D7FB4}">
   <sheetPr codeName="Sheet4">
     <tabColor rgb="FF92D050"/>
@@ -9166,7 +9816,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F6A7684-571C-4EED-95D8-7F34A7B49B6B}">
   <sheetPr codeName="Sheet5">
     <tabColor rgb="FF92D050"/>
@@ -9454,7 +10104,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6188AC2A-13AA-44F7-B850-44BEE776D85D}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -9684,7 +10334,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01F4AAFC-C1A9-47B3-B848-06156D11375D}">
   <sheetPr codeName="Sheet6">
     <tabColor rgb="FF92D050"/>
@@ -9832,7 +10482,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63EE12FB-03D5-4E75-92F5-3C993AAF3A5A}">
   <sheetPr codeName="Sheet7">
     <tabColor rgb="FF92D050"/>
@@ -9952,7 +10602,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13C6162D-ED52-4421-8B7E-2C58681ADE6F}">
   <sheetPr codeName="Sheet8">
     <tabColor rgb="FF92D050"/>
@@ -10096,7 +10746,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{208BBAD8-8992-4A11-B32C-5E8E74095072}">
   <sheetPr codeName="Sheet9">
     <tabColor rgb="FF92D050"/>
@@ -12223,7 +12873,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{700E1104-0B81-46DF-BF55-20A13EF92D67}">
   <sheetPr codeName="Sheet11">
     <tabColor theme="5"/>
@@ -12354,7 +13004,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{604C20EA-1202-4F32-9A03-50C03C9141BD}">
   <sheetPr codeName="Sheet12">
     <tabColor theme="5"/>
@@ -12455,7 +13105,182 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB0C9BC5-E2CE-4417-A398-52D4FBA952C1}">
+  <dimension ref="A1:M11"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="10.90625" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" customWidth="1"/>
+    <col min="13" max="13" width="86.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>353</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>302</v>
+      </c>
+      <c r="D1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E1" t="s">
+        <v>147</v>
+      </c>
+      <c r="F1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G1" t="s">
+        <v>179</v>
+      </c>
+      <c r="H1" t="s">
+        <v>180</v>
+      </c>
+      <c r="I1" t="s">
+        <v>1057</v>
+      </c>
+      <c r="J1" t="s">
+        <v>89</v>
+      </c>
+      <c r="K1" t="s">
+        <v>273</v>
+      </c>
+      <c r="L1" t="s">
+        <v>1058</v>
+      </c>
+      <c r="M1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>1059</v>
+      </c>
+      <c r="M2" t="s">
+        <v>1060</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>1061</v>
+      </c>
+      <c r="B3" t="s">
+        <v>540</v>
+      </c>
+      <c r="M3" t="s">
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="M4" t="s">
+        <v>1064</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>1065</v>
+      </c>
+      <c r="M5" t="s">
+        <v>1066</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>1067</v>
+      </c>
+      <c r="M6" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>1069</v>
+      </c>
+      <c r="M7" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B8" t="s">
+        <v>326</v>
+      </c>
+      <c r="M8" t="s">
+        <v>1072</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>1073</v>
+      </c>
+      <c r="M9" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B10" t="s">
+        <v>326</v>
+      </c>
+      <c r="M10" t="s">
+        <v>1076</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>49</v>
+      </c>
+      <c r="C11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" t="s">
+        <v>30</v>
+      </c>
+      <c r="E11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" t="s">
+        <v>181</v>
+      </c>
+      <c r="H11">
+        <v>2</v>
+      </c>
+      <c r="I11" t="s">
+        <v>208</v>
+      </c>
+      <c r="J11" t="s">
+        <v>91</v>
+      </c>
+      <c r="K11" t="s">
+        <v>26</v>
+      </c>
+      <c r="L11" t="s">
+        <v>100</v>
+      </c>
+      <c r="M11" t="s">
+        <v>1077</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6364318-D354-4A54-B885-C4D13BCF1553}">
   <sheetPr codeName="Sheet13">
     <tabColor theme="5"/>
@@ -12659,7 +13484,1724 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86AB462C-E7DD-41D5-B1F6-0B76A79BD546}">
+  <sheetPr codeName="Sheet10">
+    <tabColor theme="5"/>
+  </sheetPr>
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="45.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20" customWidth="1"/>
+    <col min="5" max="5" width="22.1796875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>838</v>
+      </c>
+      <c r="B2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>839</v>
+      </c>
+      <c r="B3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D3" t="s">
+        <v>99</v>
+      </c>
+      <c r="E3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>840</v>
+      </c>
+      <c r="B4" t="s">
+        <v>114</v>
+      </c>
+      <c r="C4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" t="s">
+        <v>100</v>
+      </c>
+      <c r="E4" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>841</v>
+      </c>
+      <c r="B5" t="s">
+        <v>93</v>
+      </c>
+      <c r="C5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" t="s">
+        <v>145</v>
+      </c>
+      <c r="E5" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>842</v>
+      </c>
+      <c r="B6" t="s">
+        <v>513</v>
+      </c>
+      <c r="C6" t="s">
+        <v>515</v>
+      </c>
+      <c r="D6" t="s">
+        <v>658</v>
+      </c>
+      <c r="E6" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>843</v>
+      </c>
+      <c r="B7" t="s">
+        <v>267</v>
+      </c>
+      <c r="C7" t="s">
+        <v>67</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0DA0612-5B2C-41D1-B114-8D7F9449CFCB}">
+  <sheetPr>
+    <tabColor theme="5"/>
+  </sheetPr>
+  <dimension ref="A1:C18"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="49" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" t="s">
+        <v>353</v>
+      </c>
+      <c r="C1" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>845</v>
+      </c>
+      <c r="B2" t="s">
+        <v>642</v>
+      </c>
+      <c r="C2" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>847</v>
+      </c>
+      <c r="B3" t="s">
+        <v>643</v>
+      </c>
+      <c r="C3" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>846</v>
+      </c>
+      <c r="B4" t="s">
+        <v>706</v>
+      </c>
+      <c r="C4" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>848</v>
+      </c>
+      <c r="B5" t="s">
+        <v>844</v>
+      </c>
+      <c r="C5" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>849</v>
+      </c>
+      <c r="B6" t="s">
+        <v>642</v>
+      </c>
+      <c r="C6" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>850</v>
+      </c>
+      <c r="B7" t="s">
+        <v>643</v>
+      </c>
+      <c r="C7" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>851</v>
+      </c>
+      <c r="B8" t="s">
+        <v>706</v>
+      </c>
+      <c r="C8" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>857</v>
+      </c>
+      <c r="B9" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>858</v>
+      </c>
+      <c r="B10" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>859</v>
+      </c>
+      <c r="B11" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>861</v>
+      </c>
+      <c r="B12" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>860</v>
+      </c>
+      <c r="B13" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>862</v>
+      </c>
+      <c r="B14" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>863</v>
+      </c>
+      <c r="B15" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>864</v>
+      </c>
+      <c r="B16" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>865</v>
+      </c>
+      <c r="B17" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>866</v>
+      </c>
+      <c r="B18" t="s">
+        <v>856</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF4B8566-925A-4EBE-8FA2-F566554280EF}">
+  <sheetPr codeName="Sheet14">
+    <tabColor theme="5"/>
+  </sheetPr>
+  <dimension ref="A1:E22"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="54.36328125" customWidth="1"/>
+    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.90625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E1" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" s="13" t="s">
+        <v>511</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>513</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>515</v>
+      </c>
+      <c r="D2" t="s">
+        <v>658</v>
+      </c>
+      <c r="E2" s="13" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" s="13" t="s">
+        <v>512</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>514</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>515</v>
+      </c>
+      <c r="D3" t="s">
+        <v>658</v>
+      </c>
+      <c r="E3" s="13" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="E4" s="13" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="E5" s="13" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" s="13" t="s">
+        <v>867</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="E7" s="13" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="E8" s="13" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="E9" s="13" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="E10" s="13" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="E11" s="13" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>368</v>
+      </c>
+      <c r="B12" t="s">
+        <v>376</v>
+      </c>
+      <c r="C12" t="s">
+        <v>369</v>
+      </c>
+      <c r="D12" t="s">
+        <v>369</v>
+      </c>
+      <c r="E12" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>370</v>
+      </c>
+      <c r="B13" t="s">
+        <v>377</v>
+      </c>
+      <c r="C13" t="s">
+        <v>369</v>
+      </c>
+      <c r="D13" t="s">
+        <v>369</v>
+      </c>
+      <c r="E13" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>371</v>
+      </c>
+      <c r="B14" t="s">
+        <v>379</v>
+      </c>
+      <c r="C14" t="s">
+        <v>375</v>
+      </c>
+      <c r="D14" t="s">
+        <v>369</v>
+      </c>
+      <c r="E14" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>380</v>
+      </c>
+      <c r="B15" t="s">
+        <v>378</v>
+      </c>
+      <c r="C15" t="s">
+        <v>375</v>
+      </c>
+      <c r="D15" t="s">
+        <v>369</v>
+      </c>
+      <c r="E15" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>372</v>
+      </c>
+      <c r="B16" t="s">
+        <v>381</v>
+      </c>
+      <c r="C16" t="s">
+        <v>369</v>
+      </c>
+      <c r="D16" t="s">
+        <v>369</v>
+      </c>
+      <c r="E16" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>373</v>
+      </c>
+      <c r="B17" t="s">
+        <v>382</v>
+      </c>
+      <c r="C17" t="s">
+        <v>369</v>
+      </c>
+      <c r="D17" t="s">
+        <v>369</v>
+      </c>
+      <c r="E17" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>374</v>
+      </c>
+      <c r="B18" t="s">
+        <v>383</v>
+      </c>
+      <c r="C18" t="s">
+        <v>375</v>
+      </c>
+      <c r="D18" t="s">
+        <v>369</v>
+      </c>
+      <c r="E18" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>814</v>
+      </c>
+      <c r="B19" t="s">
+        <v>384</v>
+      </c>
+      <c r="C19" t="s">
+        <v>375</v>
+      </c>
+      <c r="D19" t="s">
+        <v>369</v>
+      </c>
+      <c r="E19" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>136</v>
+      </c>
+      <c r="B20" t="s">
+        <v>151</v>
+      </c>
+      <c r="C20" t="s">
+        <v>67</v>
+      </c>
+      <c r="D20" t="s">
+        <v>67</v>
+      </c>
+      <c r="E20" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>137</v>
+      </c>
+      <c r="B21" t="s">
+        <v>163</v>
+      </c>
+      <c r="C21" t="s">
+        <v>67</v>
+      </c>
+      <c r="D21" t="s">
+        <v>67</v>
+      </c>
+      <c r="E21" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>120</v>
+      </c>
+      <c r="B22" t="s">
+        <v>96</v>
+      </c>
+      <c r="C22" t="s">
+        <v>53</v>
+      </c>
+      <c r="D22" t="s">
+        <v>53</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8162057B-52FF-4F06-A9FE-C8E0168242E3}">
+  <sheetPr codeName="Sheet15">
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="37" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="8.81640625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
+        <v>681</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>674</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>682</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
+        <v>683</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" s="1" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>684</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
+        <v>685</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="1" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>686</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
+        <v>687</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>679</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>679</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
+        <v>688</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>680</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A1" location="Index!A1" display="TestCaseName" xr:uid="{58E158FA-F610-4D72-A1CB-B39453ED1156}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32DCD494-48E9-4641-90F2-206CAB2F7041}">
+  <sheetPr codeName="Sheet16">
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="40" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E4" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D5" t="s">
+        <v>79</v>
+      </c>
+      <c r="E5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>246</v>
+      </c>
+      <c r="B6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D6" t="s">
+        <v>79</v>
+      </c>
+      <c r="E6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>246</v>
+      </c>
+      <c r="B7" t="s">
+        <v>76</v>
+      </c>
+      <c r="C7" t="s">
+        <v>146</v>
+      </c>
+      <c r="D7" t="s">
+        <v>79</v>
+      </c>
+      <c r="E7" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>274</v>
+      </c>
+      <c r="B8" t="s">
+        <v>275</v>
+      </c>
+      <c r="C8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" t="s">
+        <v>272</v>
+      </c>
+      <c r="E8" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>276</v>
+      </c>
+      <c r="B9" t="s">
+        <v>275</v>
+      </c>
+      <c r="C9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" t="s">
+        <v>272</v>
+      </c>
+      <c r="E9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>277</v>
+      </c>
+      <c r="B10" t="s">
+        <v>275</v>
+      </c>
+      <c r="C10" t="s">
+        <v>43</v>
+      </c>
+      <c r="D10" t="s">
+        <v>272</v>
+      </c>
+      <c r="E10" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>278</v>
+      </c>
+      <c r="B11" t="s">
+        <v>275</v>
+      </c>
+      <c r="C11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" t="s">
+        <v>272</v>
+      </c>
+      <c r="E11" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>362</v>
+      </c>
+      <c r="B12" t="s">
+        <v>364</v>
+      </c>
+      <c r="C12" t="s">
+        <v>365</v>
+      </c>
+      <c r="D12" t="s">
+        <v>363</v>
+      </c>
+      <c r="E12" t="s">
+        <v>273</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D72A9D9-D447-4A21-A49D-88C8132B73CE}">
+  <sheetPr codeName="Sheet17">
+    <tabColor theme="5"/>
+  </sheetPr>
+  <dimension ref="A1:D13"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="32.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.90625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D1" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C2" t="s">
+        <v>156</v>
+      </c>
+      <c r="D2" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>834</v>
+      </c>
+      <c r="B3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C3" t="s">
+        <v>695</v>
+      </c>
+      <c r="D3" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>835</v>
+      </c>
+      <c r="B4" t="s">
+        <v>154</v>
+      </c>
+      <c r="C4" t="s">
+        <v>837</v>
+      </c>
+      <c r="D4" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>836</v>
+      </c>
+      <c r="B5" t="s">
+        <v>154</v>
+      </c>
+      <c r="C5" t="s">
+        <v>837</v>
+      </c>
+      <c r="D5" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>244</v>
+      </c>
+      <c r="B6" t="s">
+        <v>154</v>
+      </c>
+      <c r="C6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>245</v>
+      </c>
+      <c r="B7" t="s">
+        <v>154</v>
+      </c>
+      <c r="C7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>152</v>
+      </c>
+      <c r="B8" t="s">
+        <v>154</v>
+      </c>
+      <c r="C8" t="s">
+        <v>156</v>
+      </c>
+      <c r="D8" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>834</v>
+      </c>
+      <c r="B9" t="s">
+        <v>154</v>
+      </c>
+      <c r="C9" t="s">
+        <v>695</v>
+      </c>
+      <c r="D9" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>835</v>
+      </c>
+      <c r="B10" t="s">
+        <v>154</v>
+      </c>
+      <c r="C10" t="s">
+        <v>837</v>
+      </c>
+      <c r="D10" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>836</v>
+      </c>
+      <c r="B11" t="s">
+        <v>154</v>
+      </c>
+      <c r="C11" t="s">
+        <v>837</v>
+      </c>
+      <c r="D11" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>244</v>
+      </c>
+      <c r="B12" t="s">
+        <v>154</v>
+      </c>
+      <c r="C12" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>245</v>
+      </c>
+      <c r="B13" t="s">
+        <v>154</v>
+      </c>
+      <c r="C13" t="s">
+        <v>27</v>
+      </c>
+      <c r="D13" t="s">
+        <v>354</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05F5A9AB-486E-4615-848C-03E69B3477F9}">
+  <sheetPr codeName="Sheet18">
+    <tabColor theme="5"/>
+  </sheetPr>
+  <dimension ref="A1:C17"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="46.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>94</v>
+      </c>
+      <c r="B7" t="s">
+        <v>95</v>
+      </c>
+      <c r="C7" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>645</v>
+      </c>
+      <c r="B8" t="s">
+        <v>646</v>
+      </c>
+      <c r="C8" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>647</v>
+      </c>
+      <c r="B9" t="s">
+        <v>648</v>
+      </c>
+      <c r="C9" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>94</v>
+      </c>
+      <c r="B11" t="s">
+        <v>95</v>
+      </c>
+      <c r="C11" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>649</v>
+      </c>
+      <c r="B12" t="s">
+        <v>650</v>
+      </c>
+      <c r="C12" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>651</v>
+      </c>
+      <c r="B13" t="s">
+        <v>652</v>
+      </c>
+      <c r="C13" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>653</v>
+      </c>
+      <c r="B14" t="s">
+        <v>812</v>
+      </c>
+      <c r="C14" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>654</v>
+      </c>
+      <c r="B15" t="s">
+        <v>813</v>
+      </c>
+      <c r="C15" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>808</v>
+      </c>
+      <c r="B16" t="s">
+        <v>810</v>
+      </c>
+      <c r="C16" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>809</v>
+      </c>
+      <c r="B17" t="s">
+        <v>811</v>
+      </c>
+      <c r="C17" t="s">
+        <v>798</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A1" location="Index!A1" display="TestCaseName" xr:uid="{AD5CC1E8-F660-4245-A0AF-526EC1CD1945}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{699F63E1-0070-48F6-AF52-8BCBFD9B07EF}">
+  <sheetPr codeName="Sheet19">
+    <tabColor theme="5"/>
+  </sheetPr>
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="61" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.81640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>816</v>
+      </c>
+      <c r="B2" t="s">
+        <v>815</v>
+      </c>
+      <c r="C2" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>817</v>
+      </c>
+      <c r="B3" t="s">
+        <v>818</v>
+      </c>
+      <c r="C3" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>800</v>
+      </c>
+      <c r="B4" t="s">
+        <v>802</v>
+      </c>
+      <c r="C4" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>801</v>
+      </c>
+      <c r="B5" t="s">
+        <v>803</v>
+      </c>
+      <c r="C5" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>806</v>
+      </c>
+      <c r="B6" t="s">
+        <v>804</v>
+      </c>
+      <c r="C6" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>807</v>
+      </c>
+      <c r="B7" t="s">
+        <v>805</v>
+      </c>
+      <c r="C7" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>157</v>
+      </c>
+      <c r="B8" t="s">
+        <v>160</v>
+      </c>
+      <c r="C8" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>158</v>
+      </c>
+      <c r="B9" t="s">
+        <v>161</v>
+      </c>
+      <c r="C9" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>159</v>
+      </c>
+      <c r="B10" t="s">
+        <v>162</v>
+      </c>
+      <c r="C10" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>700</v>
+      </c>
+      <c r="B11" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>701</v>
+      </c>
+      <c r="B12" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>702</v>
+      </c>
+      <c r="B13" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>703</v>
+      </c>
+      <c r="B14" t="s">
+        <v>699</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{783D1FEC-B865-44FA-820C-57E3FB6789F2}">
+  <sheetPr codeName="Sheet20"/>
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="30.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.453125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B6" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A1" location="Index!A1" display="Test Case Name" xr:uid="{033F2A7B-2A09-46C6-B9FE-1F3C549F93AD}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{228A5EA1-7578-437E-943F-B5DA9932AB71}">
   <dimension ref="A1:H13"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -12982,1724 +15524,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86AB462C-E7DD-41D5-B1F6-0B76A79BD546}">
-  <sheetPr codeName="Sheet10">
-    <tabColor theme="5"/>
-  </sheetPr>
-  <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="45.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.453125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20" customWidth="1"/>
-    <col min="5" max="5" width="22.1796875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C1" t="s">
-        <v>65</v>
-      </c>
-      <c r="D1" t="s">
-        <v>97</v>
-      </c>
-      <c r="E1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>838</v>
-      </c>
-      <c r="B2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D2" t="s">
-        <v>98</v>
-      </c>
-      <c r="E2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>839</v>
-      </c>
-      <c r="B3" t="s">
-        <v>113</v>
-      </c>
-      <c r="C3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D3" t="s">
-        <v>99</v>
-      </c>
-      <c r="E3" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>840</v>
-      </c>
-      <c r="B4" t="s">
-        <v>114</v>
-      </c>
-      <c r="C4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" t="s">
-        <v>100</v>
-      </c>
-      <c r="E4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>841</v>
-      </c>
-      <c r="B5" t="s">
-        <v>93</v>
-      </c>
-      <c r="C5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5" t="s">
-        <v>145</v>
-      </c>
-      <c r="E5" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>842</v>
-      </c>
-      <c r="B6" t="s">
-        <v>513</v>
-      </c>
-      <c r="C6" t="s">
-        <v>515</v>
-      </c>
-      <c r="D6" t="s">
-        <v>658</v>
-      </c>
-      <c r="E6" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>843</v>
-      </c>
-      <c r="B7" t="s">
-        <v>267</v>
-      </c>
-      <c r="C7" t="s">
-        <v>67</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0DA0612-5B2C-41D1-B114-8D7F9449CFCB}">
-  <sheetPr>
-    <tabColor theme="5"/>
-  </sheetPr>
-  <dimension ref="A1:C18"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="49" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" t="s">
-        <v>353</v>
-      </c>
-      <c r="C1" t="s">
-        <v>868</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>845</v>
-      </c>
-      <c r="B2" t="s">
-        <v>642</v>
-      </c>
-      <c r="C2" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>847</v>
-      </c>
-      <c r="B3" t="s">
-        <v>643</v>
-      </c>
-      <c r="C3" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>846</v>
-      </c>
-      <c r="B4" t="s">
-        <v>706</v>
-      </c>
-      <c r="C4" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>848</v>
-      </c>
-      <c r="B5" t="s">
-        <v>844</v>
-      </c>
-      <c r="C5" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>849</v>
-      </c>
-      <c r="B6" t="s">
-        <v>642</v>
-      </c>
-      <c r="C6" t="s">
-        <v>870</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>850</v>
-      </c>
-      <c r="B7" t="s">
-        <v>643</v>
-      </c>
-      <c r="C7" t="s">
-        <v>870</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>851</v>
-      </c>
-      <c r="B8" t="s">
-        <v>706</v>
-      </c>
-      <c r="C8" t="s">
-        <v>870</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>857</v>
-      </c>
-      <c r="B9" t="s">
-        <v>852</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>858</v>
-      </c>
-      <c r="B10" t="s">
-        <v>853</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>859</v>
-      </c>
-      <c r="B11" t="s">
-        <v>854</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>861</v>
-      </c>
-      <c r="B12" t="s">
-        <v>855</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>860</v>
-      </c>
-      <c r="B13" t="s">
-        <v>856</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>862</v>
-      </c>
-      <c r="B14" t="s">
-        <v>852</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>863</v>
-      </c>
-      <c r="B15" t="s">
-        <v>853</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>864</v>
-      </c>
-      <c r="B16" t="s">
-        <v>854</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>865</v>
-      </c>
-      <c r="B17" t="s">
-        <v>855</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>866</v>
-      </c>
-      <c r="B18" t="s">
-        <v>856</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF4B8566-925A-4EBE-8FA2-F566554280EF}">
-  <sheetPr codeName="Sheet14">
-    <tabColor theme="5"/>
-  </sheetPr>
-  <dimension ref="A1:E22"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="54.36328125" customWidth="1"/>
-    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.453125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.90625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C1" t="s">
-        <v>65</v>
-      </c>
-      <c r="D1" t="s">
-        <v>97</v>
-      </c>
-      <c r="E1" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" s="13" t="s">
-        <v>511</v>
-      </c>
-      <c r="B2" s="13" t="s">
-        <v>513</v>
-      </c>
-      <c r="C2" s="13" t="s">
-        <v>515</v>
-      </c>
-      <c r="D2" t="s">
-        <v>658</v>
-      </c>
-      <c r="E2" s="13" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" s="13" t="s">
-        <v>512</v>
-      </c>
-      <c r="B3" s="13" t="s">
-        <v>514</v>
-      </c>
-      <c r="C3" s="13" t="s">
-        <v>515</v>
-      </c>
-      <c r="D3" t="s">
-        <v>658</v>
-      </c>
-      <c r="E3" s="13" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" s="13" t="s">
-        <v>131</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="C4" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="D4" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="E4" s="13" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="B5" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="C5" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="D5" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="E5" s="13" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" s="13" t="s">
-        <v>133</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="C6" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="D6" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="E6" s="13" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" s="13" t="s">
-        <v>867</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="C7" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="D7" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="E7" s="13" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" s="13" t="s">
-        <v>140</v>
-      </c>
-      <c r="B8" s="13" t="s">
-        <v>138</v>
-      </c>
-      <c r="C8" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="D8" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="E8" s="13" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" s="13" t="s">
-        <v>141</v>
-      </c>
-      <c r="B9" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="C9" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="D9" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="E9" s="13" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" s="13" t="s">
-        <v>134</v>
-      </c>
-      <c r="B10" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="C10" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="D10" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="E10" s="13" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="B11" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="C11" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="D11" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="E11" s="13" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>368</v>
-      </c>
-      <c r="B12" t="s">
-        <v>376</v>
-      </c>
-      <c r="C12" t="s">
-        <v>369</v>
-      </c>
-      <c r="D12" t="s">
-        <v>369</v>
-      </c>
-      <c r="E12" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>370</v>
-      </c>
-      <c r="B13" t="s">
-        <v>377</v>
-      </c>
-      <c r="C13" t="s">
-        <v>369</v>
-      </c>
-      <c r="D13" t="s">
-        <v>369</v>
-      </c>
-      <c r="E13" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>371</v>
-      </c>
-      <c r="B14" t="s">
-        <v>379</v>
-      </c>
-      <c r="C14" t="s">
-        <v>375</v>
-      </c>
-      <c r="D14" t="s">
-        <v>369</v>
-      </c>
-      <c r="E14" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>380</v>
-      </c>
-      <c r="B15" t="s">
-        <v>378</v>
-      </c>
-      <c r="C15" t="s">
-        <v>375</v>
-      </c>
-      <c r="D15" t="s">
-        <v>369</v>
-      </c>
-      <c r="E15" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>372</v>
-      </c>
-      <c r="B16" t="s">
-        <v>381</v>
-      </c>
-      <c r="C16" t="s">
-        <v>369</v>
-      </c>
-      <c r="D16" t="s">
-        <v>369</v>
-      </c>
-      <c r="E16" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>373</v>
-      </c>
-      <c r="B17" t="s">
-        <v>382</v>
-      </c>
-      <c r="C17" t="s">
-        <v>369</v>
-      </c>
-      <c r="D17" t="s">
-        <v>369</v>
-      </c>
-      <c r="E17" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>374</v>
-      </c>
-      <c r="B18" t="s">
-        <v>383</v>
-      </c>
-      <c r="C18" t="s">
-        <v>375</v>
-      </c>
-      <c r="D18" t="s">
-        <v>369</v>
-      </c>
-      <c r="E18" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>814</v>
-      </c>
-      <c r="B19" t="s">
-        <v>384</v>
-      </c>
-      <c r="C19" t="s">
-        <v>375</v>
-      </c>
-      <c r="D19" t="s">
-        <v>369</v>
-      </c>
-      <c r="E19" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>136</v>
-      </c>
-      <c r="B20" t="s">
-        <v>151</v>
-      </c>
-      <c r="C20" t="s">
-        <v>67</v>
-      </c>
-      <c r="D20" t="s">
-        <v>67</v>
-      </c>
-      <c r="E20" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>137</v>
-      </c>
-      <c r="B21" t="s">
-        <v>163</v>
-      </c>
-      <c r="C21" t="s">
-        <v>67</v>
-      </c>
-      <c r="D21" t="s">
-        <v>67</v>
-      </c>
-      <c r="E21" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>120</v>
-      </c>
-      <c r="B22" t="s">
-        <v>96</v>
-      </c>
-      <c r="C22" t="s">
-        <v>53</v>
-      </c>
-      <c r="D22" t="s">
-        <v>53</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8162057B-52FF-4F06-A9FE-C8E0168242E3}">
-  <sheetPr codeName="Sheet15">
-    <tabColor rgb="FF92D050"/>
-  </sheetPr>
-  <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="37" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="8.81640625" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
-        <v>681</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>674</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>675</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
-        <v>682</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>675</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
-        <v>683</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>675</v>
-      </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="1" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
-        <v>684</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2" t="s">
-        <v>675</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="2" t="s">
-        <v>685</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="1" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" s="2" t="s">
-        <v>686</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>675</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>675</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" s="2" t="s">
-        <v>687</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>679</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>679</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" s="2" t="s">
-        <v>688</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>680</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>680</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>678</v>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="A1" location="Index!A1" display="TestCaseName" xr:uid="{58E158FA-F610-4D72-A1CB-B39453ED1156}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32DCD494-48E9-4641-90F2-206CAB2F7041}">
-  <sheetPr codeName="Sheet16">
-    <tabColor rgb="FF92D050"/>
-  </sheetPr>
-  <dimension ref="A1:E12"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="40" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.1796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C1" t="s">
-        <v>63</v>
-      </c>
-      <c r="D1" t="s">
-        <v>62</v>
-      </c>
-      <c r="E1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" t="s">
-        <v>78</v>
-      </c>
-      <c r="E2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>71</v>
-      </c>
-      <c r="B3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D3" t="s">
-        <v>78</v>
-      </c>
-      <c r="E3" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>74</v>
-      </c>
-      <c r="B4" t="s">
-        <v>70</v>
-      </c>
-      <c r="C4" t="s">
-        <v>73</v>
-      </c>
-      <c r="D4" t="s">
-        <v>78</v>
-      </c>
-      <c r="E4" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>75</v>
-      </c>
-      <c r="B5" t="s">
-        <v>76</v>
-      </c>
-      <c r="C5" t="s">
-        <v>64</v>
-      </c>
-      <c r="D5" t="s">
-        <v>79</v>
-      </c>
-      <c r="E5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>246</v>
-      </c>
-      <c r="B6" t="s">
-        <v>76</v>
-      </c>
-      <c r="C6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D6" t="s">
-        <v>79</v>
-      </c>
-      <c r="E6" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>246</v>
-      </c>
-      <c r="B7" t="s">
-        <v>76</v>
-      </c>
-      <c r="C7" t="s">
-        <v>146</v>
-      </c>
-      <c r="D7" t="s">
-        <v>79</v>
-      </c>
-      <c r="E7" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>274</v>
-      </c>
-      <c r="B8" t="s">
-        <v>275</v>
-      </c>
-      <c r="C8" t="s">
-        <v>26</v>
-      </c>
-      <c r="D8" t="s">
-        <v>272</v>
-      </c>
-      <c r="E8" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>276</v>
-      </c>
-      <c r="B9" t="s">
-        <v>275</v>
-      </c>
-      <c r="C9" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9" t="s">
-        <v>272</v>
-      </c>
-      <c r="E9" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>277</v>
-      </c>
-      <c r="B10" t="s">
-        <v>275</v>
-      </c>
-      <c r="C10" t="s">
-        <v>43</v>
-      </c>
-      <c r="D10" t="s">
-        <v>272</v>
-      </c>
-      <c r="E10" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>278</v>
-      </c>
-      <c r="B11" t="s">
-        <v>275</v>
-      </c>
-      <c r="C11" t="s">
-        <v>23</v>
-      </c>
-      <c r="D11" t="s">
-        <v>272</v>
-      </c>
-      <c r="E11" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>362</v>
-      </c>
-      <c r="B12" t="s">
-        <v>364</v>
-      </c>
-      <c r="C12" t="s">
-        <v>365</v>
-      </c>
-      <c r="D12" t="s">
-        <v>363</v>
-      </c>
-      <c r="E12" t="s">
-        <v>273</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D72A9D9-D447-4A21-A49D-88C8132B73CE}">
-  <sheetPr codeName="Sheet17">
-    <tabColor theme="5"/>
-  </sheetPr>
-  <dimension ref="A1:D13"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="32.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.90625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C1" t="s">
-        <v>65</v>
-      </c>
-      <c r="D1" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>152</v>
-      </c>
-      <c r="B2" t="s">
-        <v>154</v>
-      </c>
-      <c r="C2" t="s">
-        <v>156</v>
-      </c>
-      <c r="D2" t="s">
-        <v>871</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>834</v>
-      </c>
-      <c r="B3" t="s">
-        <v>154</v>
-      </c>
-      <c r="C3" t="s">
-        <v>695</v>
-      </c>
-      <c r="D3" t="s">
-        <v>871</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>835</v>
-      </c>
-      <c r="B4" t="s">
-        <v>154</v>
-      </c>
-      <c r="C4" t="s">
-        <v>837</v>
-      </c>
-      <c r="D4" t="s">
-        <v>871</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>836</v>
-      </c>
-      <c r="B5" t="s">
-        <v>154</v>
-      </c>
-      <c r="C5" t="s">
-        <v>837</v>
-      </c>
-      <c r="D5" t="s">
-        <v>871</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>244</v>
-      </c>
-      <c r="B6" t="s">
-        <v>154</v>
-      </c>
-      <c r="C6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D6" t="s">
-        <v>871</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>245</v>
-      </c>
-      <c r="B7" t="s">
-        <v>154</v>
-      </c>
-      <c r="C7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7" t="s">
-        <v>871</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>152</v>
-      </c>
-      <c r="B8" t="s">
-        <v>154</v>
-      </c>
-      <c r="C8" t="s">
-        <v>156</v>
-      </c>
-      <c r="D8" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>834</v>
-      </c>
-      <c r="B9" t="s">
-        <v>154</v>
-      </c>
-      <c r="C9" t="s">
-        <v>695</v>
-      </c>
-      <c r="D9" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>835</v>
-      </c>
-      <c r="B10" t="s">
-        <v>154</v>
-      </c>
-      <c r="C10" t="s">
-        <v>837</v>
-      </c>
-      <c r="D10" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>836</v>
-      </c>
-      <c r="B11" t="s">
-        <v>154</v>
-      </c>
-      <c r="C11" t="s">
-        <v>837</v>
-      </c>
-      <c r="D11" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>244</v>
-      </c>
-      <c r="B12" t="s">
-        <v>154</v>
-      </c>
-      <c r="C12" t="s">
-        <v>30</v>
-      </c>
-      <c r="D12" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>245</v>
-      </c>
-      <c r="B13" t="s">
-        <v>154</v>
-      </c>
-      <c r="C13" t="s">
-        <v>27</v>
-      </c>
-      <c r="D13" t="s">
-        <v>354</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05F5A9AB-486E-4615-848C-03E69B3477F9}">
-  <sheetPr codeName="Sheet18">
-    <tabColor theme="5"/>
-  </sheetPr>
-  <dimension ref="A1:C17"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="46.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.6328125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>94</v>
-      </c>
-      <c r="B7" t="s">
-        <v>95</v>
-      </c>
-      <c r="C7" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>645</v>
-      </c>
-      <c r="B8" t="s">
-        <v>646</v>
-      </c>
-      <c r="C8" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>647</v>
-      </c>
-      <c r="B9" t="s">
-        <v>648</v>
-      </c>
-      <c r="C9" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>94</v>
-      </c>
-      <c r="B11" t="s">
-        <v>95</v>
-      </c>
-      <c r="C11" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>649</v>
-      </c>
-      <c r="B12" t="s">
-        <v>650</v>
-      </c>
-      <c r="C12" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>651</v>
-      </c>
-      <c r="B13" t="s">
-        <v>652</v>
-      </c>
-      <c r="C13" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>653</v>
-      </c>
-      <c r="B14" t="s">
-        <v>812</v>
-      </c>
-      <c r="C14" t="s">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>654</v>
-      </c>
-      <c r="B15" t="s">
-        <v>813</v>
-      </c>
-      <c r="C15" t="s">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>808</v>
-      </c>
-      <c r="B16" t="s">
-        <v>810</v>
-      </c>
-      <c r="C16" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>809</v>
-      </c>
-      <c r="B17" t="s">
-        <v>811</v>
-      </c>
-      <c r="C17" t="s">
-        <v>798</v>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="A1" location="Index!A1" display="TestCaseName" xr:uid="{AD5CC1E8-F660-4245-A0AF-526EC1CD1945}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{699F63E1-0070-48F6-AF52-8BCBFD9B07EF}">
-  <sheetPr codeName="Sheet19">
-    <tabColor theme="5"/>
-  </sheetPr>
-  <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="61" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.81640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C1" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>816</v>
-      </c>
-      <c r="B2" t="s">
-        <v>815</v>
-      </c>
-      <c r="C2" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>817</v>
-      </c>
-      <c r="B3" t="s">
-        <v>818</v>
-      </c>
-      <c r="C3" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>800</v>
-      </c>
-      <c r="B4" t="s">
-        <v>802</v>
-      </c>
-      <c r="C4" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>801</v>
-      </c>
-      <c r="B5" t="s">
-        <v>803</v>
-      </c>
-      <c r="C5" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>806</v>
-      </c>
-      <c r="B6" t="s">
-        <v>804</v>
-      </c>
-      <c r="C6" t="s">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>807</v>
-      </c>
-      <c r="B7" t="s">
-        <v>805</v>
-      </c>
-      <c r="C7" t="s">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>157</v>
-      </c>
-      <c r="B8" t="s">
-        <v>160</v>
-      </c>
-      <c r="C8" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>158</v>
-      </c>
-      <c r="B9" t="s">
-        <v>161</v>
-      </c>
-      <c r="C9" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>159</v>
-      </c>
-      <c r="B10" t="s">
-        <v>162</v>
-      </c>
-      <c r="C10" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>700</v>
-      </c>
-      <c r="B11" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>701</v>
-      </c>
-      <c r="B12" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>702</v>
-      </c>
-      <c r="B13" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>703</v>
-      </c>
-      <c r="B14" t="s">
-        <v>699</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{783D1FEC-B865-44FA-820C-57E3FB6789F2}">
-  <sheetPr codeName="Sheet20"/>
-  <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="30.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.453125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="B1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>61</v>
-      </c>
-      <c r="B3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>58</v>
-      </c>
-      <c r="B4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>59</v>
-      </c>
-      <c r="B5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>56</v>
-      </c>
-      <c r="B6" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>57</v>
-      </c>
-      <c r="B7" t="s">
-        <v>30</v>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="A1" location="Index!A1" display="Test Case Name" xr:uid="{033F2A7B-2A09-46C6-B9FE-1F3C549F93AD}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81503B49-E101-4423-8FFF-B866835D92EC}">
   <sheetPr codeName="Sheet21"/>
   <dimension ref="A1:B5"/>
@@ -14754,306 +15579,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4A529B9-903C-45A2-901F-9D341955071D}">
-  <dimension ref="A1:D20"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="89.81640625" customWidth="1"/>
-    <col min="2" max="2" width="15.453125" customWidth="1"/>
-    <col min="3" max="3" width="17.453125" customWidth="1"/>
-    <col min="4" max="4" width="13.6328125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" t="s">
-        <v>353</v>
-      </c>
-      <c r="C1" t="s">
-        <v>734</v>
-      </c>
-      <c r="D1" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>988</v>
-      </c>
-      <c r="B2" t="s">
-        <v>779</v>
-      </c>
-      <c r="C2" t="s">
-        <v>989</v>
-      </c>
-      <c r="D2" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>990</v>
-      </c>
-      <c r="B3" t="s">
-        <v>747</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>991</v>
-      </c>
-      <c r="D3" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>992</v>
-      </c>
-      <c r="B4" t="s">
-        <v>993</v>
-      </c>
-      <c r="C4" t="s">
-        <v>994</v>
-      </c>
-      <c r="D4" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>995</v>
-      </c>
-      <c r="B5" t="s">
-        <v>996</v>
-      </c>
-      <c r="C5" t="s">
-        <v>764</v>
-      </c>
-      <c r="D5" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>997</v>
-      </c>
-      <c r="B6" t="s">
-        <v>998</v>
-      </c>
-      <c r="C6" t="s">
-        <v>998</v>
-      </c>
-      <c r="D6" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>999</v>
-      </c>
-      <c r="B7" t="s">
-        <v>1000</v>
-      </c>
-      <c r="C7" t="s">
-        <v>1001</v>
-      </c>
-      <c r="D7" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>1002</v>
-      </c>
-      <c r="B8" t="s">
-        <v>1003</v>
-      </c>
-      <c r="C8" t="s">
-        <v>1003</v>
-      </c>
-      <c r="D8" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>1004</v>
-      </c>
-      <c r="B9" t="s">
-        <v>1005</v>
-      </c>
-      <c r="C9" t="s">
-        <v>1006</v>
-      </c>
-      <c r="D9" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>1007</v>
-      </c>
-      <c r="B10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10" t="s">
-        <v>1008</v>
-      </c>
-      <c r="D10" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>1009</v>
-      </c>
-      <c r="B11" t="s">
-        <v>1010</v>
-      </c>
-      <c r="C11" t="s">
-        <v>1011</v>
-      </c>
-      <c r="D11" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>1012</v>
-      </c>
-      <c r="B12" t="s">
-        <v>1013</v>
-      </c>
-      <c r="C12" t="s">
-        <v>1013</v>
-      </c>
-      <c r="D12" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>1014</v>
-      </c>
-      <c r="B13" t="s">
-        <v>1015</v>
-      </c>
-      <c r="C13" t="s">
-        <v>1011</v>
-      </c>
-      <c r="D13" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>1016</v>
-      </c>
-      <c r="B14" t="s">
-        <v>1017</v>
-      </c>
-      <c r="C14" t="s">
-        <v>1018</v>
-      </c>
-      <c r="D14" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>1019</v>
-      </c>
-      <c r="B15" t="s">
-        <v>1020</v>
-      </c>
-      <c r="C15" t="s">
-        <v>155</v>
-      </c>
-      <c r="D15" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>1021</v>
-      </c>
-      <c r="B16" t="s">
-        <v>67</v>
-      </c>
-      <c r="C16" t="s">
-        <v>67</v>
-      </c>
-      <c r="D16" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>1022</v>
-      </c>
-      <c r="B17" t="s">
-        <v>155</v>
-      </c>
-      <c r="C17" t="s">
-        <v>1023</v>
-      </c>
-      <c r="D17" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>1024</v>
-      </c>
-      <c r="B18" t="s">
-        <v>1025</v>
-      </c>
-      <c r="C18" t="s">
-        <v>1026</v>
-      </c>
-      <c r="D18" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>1027</v>
-      </c>
-      <c r="B19" t="s">
-        <v>1028</v>
-      </c>
-      <c r="C19" t="s">
-        <v>1028</v>
-      </c>
-      <c r="D19" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>1029</v>
-      </c>
-      <c r="B20" t="s">
-        <v>1030</v>
-      </c>
-      <c r="C20" t="s">
-        <v>1031</v>
-      </c>
-      <c r="D20" t="s">
-        <v>738</v>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="C3" r:id="rId1" xr:uid="{0BDD38D8-2559-4808-96F6-AF1B036AFB43}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CCEF9F3-3285-454F-A311-2FAE775A4BE5}">
   <sheetPr codeName="Sheet22">
     <tabColor rgb="FF92D050"/>
@@ -15517,6 +16043,305 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4A529B9-903C-45A2-901F-9D341955071D}">
+  <dimension ref="A1:D20"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="89.81640625" customWidth="1"/>
+    <col min="2" max="2" width="15.453125" customWidth="1"/>
+    <col min="3" max="3" width="17.453125" customWidth="1"/>
+    <col min="4" max="4" width="13.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" t="s">
+        <v>353</v>
+      </c>
+      <c r="C1" t="s">
+        <v>734</v>
+      </c>
+      <c r="D1" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>988</v>
+      </c>
+      <c r="B2" t="s">
+        <v>779</v>
+      </c>
+      <c r="C2" t="s">
+        <v>989</v>
+      </c>
+      <c r="D2" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>990</v>
+      </c>
+      <c r="B3" t="s">
+        <v>747</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>991</v>
+      </c>
+      <c r="D3" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>992</v>
+      </c>
+      <c r="B4" t="s">
+        <v>993</v>
+      </c>
+      <c r="C4" t="s">
+        <v>994</v>
+      </c>
+      <c r="D4" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>995</v>
+      </c>
+      <c r="B5" t="s">
+        <v>996</v>
+      </c>
+      <c r="C5" t="s">
+        <v>764</v>
+      </c>
+      <c r="D5" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>997</v>
+      </c>
+      <c r="B6" t="s">
+        <v>998</v>
+      </c>
+      <c r="C6" t="s">
+        <v>998</v>
+      </c>
+      <c r="D6" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>999</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1000</v>
+      </c>
+      <c r="C7" t="s">
+        <v>1001</v>
+      </c>
+      <c r="D7" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1003</v>
+      </c>
+      <c r="C8" t="s">
+        <v>1003</v>
+      </c>
+      <c r="D8" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1005</v>
+      </c>
+      <c r="C9" t="s">
+        <v>1006</v>
+      </c>
+      <c r="D9" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" t="s">
+        <v>1008</v>
+      </c>
+      <c r="D10" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B11" t="s">
+        <v>1010</v>
+      </c>
+      <c r="C11" t="s">
+        <v>1011</v>
+      </c>
+      <c r="D11" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B12" t="s">
+        <v>1013</v>
+      </c>
+      <c r="C12" t="s">
+        <v>1013</v>
+      </c>
+      <c r="D12" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B13" t="s">
+        <v>1015</v>
+      </c>
+      <c r="C13" t="s">
+        <v>1011</v>
+      </c>
+      <c r="D13" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>1016</v>
+      </c>
+      <c r="B14" t="s">
+        <v>1017</v>
+      </c>
+      <c r="C14" t="s">
+        <v>1018</v>
+      </c>
+      <c r="D14" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B15" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C15" t="s">
+        <v>155</v>
+      </c>
+      <c r="D15" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B16" t="s">
+        <v>67</v>
+      </c>
+      <c r="C16" t="s">
+        <v>67</v>
+      </c>
+      <c r="D16" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B17" t="s">
+        <v>155</v>
+      </c>
+      <c r="C17" t="s">
+        <v>1023</v>
+      </c>
+      <c r="D17" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>1024</v>
+      </c>
+      <c r="B18" t="s">
+        <v>1025</v>
+      </c>
+      <c r="C18" t="s">
+        <v>1026</v>
+      </c>
+      <c r="D18" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B19" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C19" t="s">
+        <v>1028</v>
+      </c>
+      <c r="D19" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>1029</v>
+      </c>
+      <c r="B20" t="s">
+        <v>1030</v>
+      </c>
+      <c r="C20" t="s">
+        <v>1031</v>
+      </c>
+      <c r="D20" t="s">
+        <v>738</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C3" r:id="rId1" xr:uid="{0BDD38D8-2559-4808-96F6-AF1B036AFB43}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38E2CB3A-76BE-454A-8CED-01A84C1CCF2F}">
   <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -15747,7 +16572,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE3050C8-3A8D-4DE1-9C22-09145670512E}">
   <dimension ref="A1:F11"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -15988,7 +16813,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8004406F-9BB5-44CC-B5FD-6AB51EA63268}">
   <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -16062,7 +16887,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BDEB086-7FEB-4B39-87A9-1F088DACEF5D}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -16247,52 +17072,4 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F523F3BF-8164-44E1-977A-66026445142F}">
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="38.6328125" customWidth="1"/>
-    <col min="2" max="2" width="11.08984375" customWidth="1"/>
-    <col min="3" max="3" width="10.90625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" t="s">
-        <v>273</v>
-      </c>
-      <c r="C1" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>767</v>
-      </c>
-      <c r="B2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C2" t="s">
-        <v>768</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>770</v>
-      </c>
-      <c r="B3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" t="s">
-        <v>769</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/Data Files/TestData.xlsx
+++ b/Data Files/TestData.xlsx
@@ -8,57 +8,58 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gitRemoteViz\AccessWeb\Data Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D4CF4BE-3382-4862-B4C1-45A7850B092C}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03F264E2-7EB9-4954-B52A-658CE795F572}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10560" tabRatio="954" activeTab="1" xr2:uid="{C6F85985-84AE-4DCB-8550-9B2F16782E4E}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10560" tabRatio="954" firstSheet="1" activeTab="1" xr2:uid="{C6F85985-84AE-4DCB-8550-9B2F16782E4E}"/>
   </bookViews>
   <sheets>
     <sheet name="Index" sheetId="26" r:id="rId1"/>
-    <sheet name="MultiFileFolderOps" sheetId="48" r:id="rId2"/>
-    <sheet name="Audit Logs" sheetId="47" r:id="rId3"/>
-    <sheet name="ChangePasswd" sheetId="46" r:id="rId4"/>
-    <sheet name="AppComposerNew" sheetId="44" r:id="rId5"/>
-    <sheet name="AppComposer" sheetId="45" r:id="rId6"/>
-    <sheet name="FilesTableCols " sheetId="43" r:id="rId7"/>
-    <sheet name="FileViewer2020.4" sheetId="41" r:id="rId8"/>
-    <sheet name="ManageBookMark" sheetId="40" r:id="rId9"/>
-    <sheet name="2020.4" sheetId="39" r:id="rId10"/>
-    <sheet name="FileViewerJobs" sheetId="37" r:id="rId11"/>
-    <sheet name="Generic_Actions" sheetId="36" r:id="rId12"/>
-    <sheet name="Access_Management" sheetId="32" r:id="rId13"/>
-    <sheet name="Preferences" sheetId="33" r:id="rId14"/>
-    <sheet name="JobsTableCols" sheetId="29" r:id="rId15"/>
-    <sheet name="Cluster_Registration" sheetId="28" r:id="rId16"/>
-    <sheet name="JobDetails" sheetId="30" r:id="rId17"/>
-    <sheet name="JobMonitoringGeneric" sheetId="27" r:id="rId18"/>
-    <sheet name="ViewDetailsForNonOwner" sheetId="23" r:id="rId19"/>
-    <sheet name="ProfileSubmissions" sheetId="21" r:id="rId20"/>
-    <sheet name="ProfileOperations" sheetId="14" r:id="rId21"/>
-    <sheet name="JobAction" sheetId="5" r:id="rId22"/>
-    <sheet name="JobArrayAction" sheetId="31" r:id="rId23"/>
-    <sheet name="JobActionNotJobOwner" sheetId="20" r:id="rId24"/>
-    <sheet name="JobActionIcon" sheetId="18" r:id="rId25"/>
-    <sheet name="JobActionIconNotJobOwner" sheetId="24" r:id="rId26"/>
-    <sheet name="JS-Latest" sheetId="16" r:id="rId27"/>
-    <sheet name="BookMarks" sheetId="17" r:id="rId28"/>
-    <sheet name="JobSubmission-Folder operations" sheetId="12" r:id="rId29"/>
-    <sheet name="FolderOperations" sheetId="11" r:id="rId30"/>
-    <sheet name="JobSubmission-File operations" sheetId="13" r:id="rId31"/>
-    <sheet name="FileTab_GenericTC" sheetId="42" r:id="rId32"/>
-    <sheet name="FileOperations" sheetId="9" r:id="rId33"/>
-    <sheet name="LoginData" sheetId="1" r:id="rId34"/>
-    <sheet name="JobFilters" sheetId="8" r:id="rId35"/>
-    <sheet name="FileViewerOps" sheetId="15" r:id="rId36"/>
-    <sheet name="CreateFolder" sheetId="2" r:id="rId37"/>
-    <sheet name="CreateFile" sheetId="3" r:id="rId38"/>
-    <sheet name="CompletedJobsFolder" sheetId="7" r:id="rId39"/>
-    <sheet name="RunningFolder" sheetId="6" r:id="rId40"/>
-    <sheet name="JobFiltersSavedFilters" sheetId="19" r:id="rId41"/>
+    <sheet name="HiddenFileFolder" sheetId="49" r:id="rId2"/>
+    <sheet name="MultiFileFolderOps" sheetId="48" r:id="rId3"/>
+    <sheet name="Audit Logs" sheetId="47" r:id="rId4"/>
+    <sheet name="ChangePasswd" sheetId="46" r:id="rId5"/>
+    <sheet name="AppComposerNew" sheetId="44" r:id="rId6"/>
+    <sheet name="AppComposer" sheetId="45" r:id="rId7"/>
+    <sheet name="FilesTableCols " sheetId="43" r:id="rId8"/>
+    <sheet name="FileViewer2020.4" sheetId="41" r:id="rId9"/>
+    <sheet name="ManageBookMark" sheetId="40" r:id="rId10"/>
+    <sheet name="2020.4" sheetId="39" r:id="rId11"/>
+    <sheet name="FileViewerJobs" sheetId="37" r:id="rId12"/>
+    <sheet name="Generic_Actions" sheetId="36" r:id="rId13"/>
+    <sheet name="Access_Management" sheetId="32" r:id="rId14"/>
+    <sheet name="Preferences" sheetId="33" r:id="rId15"/>
+    <sheet name="JobsTableCols" sheetId="29" r:id="rId16"/>
+    <sheet name="Cluster_Registration" sheetId="28" r:id="rId17"/>
+    <sheet name="JobDetails" sheetId="30" r:id="rId18"/>
+    <sheet name="JobMonitoringGeneric" sheetId="27" r:id="rId19"/>
+    <sheet name="ViewDetailsForNonOwner" sheetId="23" r:id="rId20"/>
+    <sheet name="ProfileSubmissions" sheetId="21" r:id="rId21"/>
+    <sheet name="ProfileOperations" sheetId="14" r:id="rId22"/>
+    <sheet name="JobAction" sheetId="5" r:id="rId23"/>
+    <sheet name="JobArrayAction" sheetId="31" r:id="rId24"/>
+    <sheet name="JobActionNotJobOwner" sheetId="20" r:id="rId25"/>
+    <sheet name="JobActionIcon" sheetId="18" r:id="rId26"/>
+    <sheet name="JobActionIconNotJobOwner" sheetId="24" r:id="rId27"/>
+    <sheet name="JS-Latest" sheetId="16" r:id="rId28"/>
+    <sheet name="BookMarks" sheetId="17" r:id="rId29"/>
+    <sheet name="JobSubmission-Folder operations" sheetId="12" r:id="rId30"/>
+    <sheet name="FolderOperations" sheetId="11" r:id="rId31"/>
+    <sheet name="JobSubmission-File operations" sheetId="13" r:id="rId32"/>
+    <sheet name="FileTab_GenericTC" sheetId="42" r:id="rId33"/>
+    <sheet name="FileOperations" sheetId="9" r:id="rId34"/>
+    <sheet name="LoginData" sheetId="1" r:id="rId35"/>
+    <sheet name="JobFilters" sheetId="8" r:id="rId36"/>
+    <sheet name="FileViewerOps" sheetId="15" r:id="rId37"/>
+    <sheet name="CreateFolder" sheetId="2" r:id="rId38"/>
+    <sheet name="CreateFile" sheetId="3" r:id="rId39"/>
+    <sheet name="CompletedJobsFolder" sheetId="7" r:id="rId40"/>
+    <sheet name="RunningFolder" sheetId="6" r:id="rId41"/>
+    <sheet name="JobFiltersSavedFilters" sheetId="19" r:id="rId42"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="26" hidden="1">'JS-Latest'!$A$1:$G$56</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">ProfileOperations!$A$1:$G$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">ProfileSubmissions!$A$1:$G$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="27" hidden="1">'JS-Latest'!$A$1:$G$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">ProfileOperations!$A$1:$G$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">ProfileSubmissions!$A$1:$G$37</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -78,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3494" uniqueCount="1147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3558" uniqueCount="1158">
   <si>
     <t>username</t>
   </si>
@@ -3521,6 +3522,39 @@
   </si>
   <si>
     <t>Test case to make sure the Input files and folders are displayed under Input section and the user is able to delete by selecting the multiple files and folders</t>
+  </si>
+  <si>
+    <t>RFB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">view hidden file and folders  - files tab - jobs page rfb </t>
+  </si>
+  <si>
+    <t xml:space="preserve">view hidden file and folders  - running  tab </t>
+  </si>
+  <si>
+    <t xml:space="preserve">view hidden file and folders  - output tab </t>
+  </si>
+  <si>
+    <t xml:space="preserve">view hidden file and folders  - input tab </t>
+  </si>
+  <si>
+    <t xml:space="preserve">view hidden file and folders  - files tab </t>
+  </si>
+  <si>
+    <t>FilesTab</t>
+  </si>
+  <si>
+    <t>prefValue</t>
+  </si>
+  <si>
+    <t>user</t>
+  </si>
+  <si>
+    <t>normal</t>
+  </si>
+  <si>
+    <t>admin</t>
   </si>
 </sst>
 </file>
@@ -3609,7 +3643,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -3647,13 +3681,58 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -3688,6 +3767,15 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Accent5" xfId="1" builtinId="45"/>
@@ -4240,6 +4328,193 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BDEB086-7FEB-4B39-87A9-1F088DACEF5D}">
+  <sheetPr>
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
+  <dimension ref="A1:D12"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="56.453125" customWidth="1"/>
+    <col min="2" max="2" width="24.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.54296875" customWidth="1"/>
+    <col min="4" max="4" width="14.6328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C1" t="s">
+        <v>255</v>
+      </c>
+      <c r="D1" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B2" t="s">
+        <v>259</v>
+      </c>
+      <c r="C2" t="s">
+        <v>256</v>
+      </c>
+      <c r="D2" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>248</v>
+      </c>
+      <c r="B3" t="s">
+        <v>259</v>
+      </c>
+      <c r="C3" t="s">
+        <v>256</v>
+      </c>
+      <c r="D3" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>249</v>
+      </c>
+      <c r="B4" t="s">
+        <v>250</v>
+      </c>
+      <c r="C4" t="s">
+        <v>256</v>
+      </c>
+      <c r="D4" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>251</v>
+      </c>
+      <c r="B5" t="s">
+        <v>252</v>
+      </c>
+      <c r="C5" t="s">
+        <v>256</v>
+      </c>
+      <c r="D5" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>253</v>
+      </c>
+      <c r="B6" t="s">
+        <v>250</v>
+      </c>
+      <c r="C6" t="s">
+        <v>257</v>
+      </c>
+      <c r="D6" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>655</v>
+      </c>
+      <c r="C7" t="s">
+        <v>656</v>
+      </c>
+      <c r="D7" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>657</v>
+      </c>
+      <c r="B8" t="s">
+        <v>540</v>
+      </c>
+      <c r="C8" t="s">
+        <v>256</v>
+      </c>
+      <c r="D8" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>780</v>
+      </c>
+      <c r="B9" t="s">
+        <v>781</v>
+      </c>
+      <c r="C9" t="s">
+        <v>782</v>
+      </c>
+      <c r="D9" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>784</v>
+      </c>
+      <c r="B10" t="s">
+        <v>785</v>
+      </c>
+      <c r="C10" t="s">
+        <v>783</v>
+      </c>
+      <c r="D10" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>786</v>
+      </c>
+      <c r="B11" t="s">
+        <v>787</v>
+      </c>
+      <c r="C11" t="s">
+        <v>257</v>
+      </c>
+      <c r="D11" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>789</v>
+      </c>
+      <c r="B12" t="s">
+        <v>788</v>
+      </c>
+      <c r="C12" t="s">
+        <v>257</v>
+      </c>
+      <c r="D12" t="s">
+        <v>690</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A1" location="Index!A1" display="TestCaseName" xr:uid="{7DBFE464-6614-48D5-A3DF-EA70153B35D9}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F523F3BF-8164-44E1-977A-66026445142F}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -4287,7 +4562,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4567093D-A8D5-4E03-9534-579CE219E49C}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -4627,7 +4902,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4B5724D-5463-4FCF-A4F1-F5DFAB6E3F70}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -4684,7 +4959,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55DC2C27-8A96-4A23-BB21-23846DE78349}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -4977,7 +5252,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{484BDA10-16FC-473B-B01F-8455443B2C0A}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -5149,7 +5424,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CE8C224-BA72-4C4C-B7BF-5463A9EB02C3}">
   <dimension ref="A1:F25"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -5670,7 +5945,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D482266D-B90F-4B77-ADCD-DBA0EB5AE431}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -6155,7 +6430,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B160D41-22A7-4DDD-97BB-D99E5654BA01}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -6553,7 +6828,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{414B5370-5029-483B-916B-4E563C4D6F93}">
   <dimension ref="A1:C15"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -6736,7 +7011,317 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CAADB6C-9565-42AA-8291-A315CEC7193D}">
+  <dimension ref="A1:D21"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="46" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1154</v>
+      </c>
+      <c r="C1" t="s">
+        <v>353</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1155</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" s="28" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B2" s="28" t="b">
+        <v>1</v>
+      </c>
+      <c r="C2" s="28" t="s">
+        <v>1153</v>
+      </c>
+      <c r="D2" t="s">
+        <v>1156</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" s="27" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B3" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="C3" s="27" t="s">
+        <v>1153</v>
+      </c>
+      <c r="D3" t="s">
+        <v>1156</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" s="27" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B4" s="27" t="b">
+        <v>1</v>
+      </c>
+      <c r="C4" s="27" t="s">
+        <v>304</v>
+      </c>
+      <c r="D4" t="s">
+        <v>1156</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" s="27" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B5" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="C5" s="27" t="s">
+        <v>304</v>
+      </c>
+      <c r="D5" t="s">
+        <v>1156</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" s="27" t="s">
+        <v>1150</v>
+      </c>
+      <c r="B6" s="27" t="b">
+        <v>1</v>
+      </c>
+      <c r="C6" s="27" t="s">
+        <v>310</v>
+      </c>
+      <c r="D6" t="s">
+        <v>1156</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" s="27" t="s">
+        <v>1150</v>
+      </c>
+      <c r="B7" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="C7" s="27" t="s">
+        <v>310</v>
+      </c>
+      <c r="D7" t="s">
+        <v>1156</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" s="27" t="s">
+        <v>1149</v>
+      </c>
+      <c r="B8" s="27" t="b">
+        <v>1</v>
+      </c>
+      <c r="C8" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" t="s">
+        <v>1156</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" s="27" t="s">
+        <v>1149</v>
+      </c>
+      <c r="B9" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="C9" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" t="s">
+        <v>1156</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" s="27" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B10" s="27" t="b">
+        <v>1</v>
+      </c>
+      <c r="C10" s="27" t="s">
+        <v>1147</v>
+      </c>
+      <c r="D10" t="s">
+        <v>1156</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="26" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B11" s="26" t="b">
+        <v>0</v>
+      </c>
+      <c r="C11" s="26" t="s">
+        <v>1147</v>
+      </c>
+      <c r="D11" t="s">
+        <v>1156</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" s="28" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B12" s="28" t="b">
+        <v>1</v>
+      </c>
+      <c r="C12" s="28" t="s">
+        <v>582</v>
+      </c>
+      <c r="D12" t="s">
+        <v>1157</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" s="27" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B13" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="C13" s="27" t="s">
+        <v>582</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1157</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14" s="27" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B14" s="27" t="b">
+        <v>1</v>
+      </c>
+      <c r="C14" s="27" t="s">
+        <v>304</v>
+      </c>
+      <c r="D14" t="s">
+        <v>1157</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15" s="27" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B15" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="C15" s="27" t="s">
+        <v>304</v>
+      </c>
+      <c r="D15" t="s">
+        <v>1157</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A16" s="27" t="s">
+        <v>1150</v>
+      </c>
+      <c r="B16" s="27" t="b">
+        <v>1</v>
+      </c>
+      <c r="C16" s="27" t="s">
+        <v>310</v>
+      </c>
+      <c r="D16" t="s">
+        <v>1157</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" s="27" t="s">
+        <v>1150</v>
+      </c>
+      <c r="B17" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="C17" s="27" t="s">
+        <v>310</v>
+      </c>
+      <c r="D17" t="s">
+        <v>1157</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" s="27" t="s">
+        <v>1149</v>
+      </c>
+      <c r="B18" s="27" t="b">
+        <v>1</v>
+      </c>
+      <c r="C18" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="D18" t="s">
+        <v>1157</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" s="27" t="s">
+        <v>1149</v>
+      </c>
+      <c r="B19" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="C19" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="D19" t="s">
+        <v>1157</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" s="27" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B20" s="27" t="b">
+        <v>1</v>
+      </c>
+      <c r="C20" s="27" t="s">
+        <v>1147</v>
+      </c>
+      <c r="D20" t="s">
+        <v>1157</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="26" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B21" s="26" t="b">
+        <v>0</v>
+      </c>
+      <c r="C21" s="26" t="s">
+        <v>1147</v>
+      </c>
+      <c r="D21" t="s">
+        <v>1157</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07DE01A5-2C8B-4355-8451-CE73E53961BB}">
   <sheetPr codeName="Sheet2">
     <tabColor rgb="FF92D050"/>
@@ -6979,653 +7564,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C2E8DB6-985C-4A4D-B54D-754B4AB198CD}">
-  <dimension ref="A1:E37"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="146.90625" customWidth="1"/>
-    <col min="2" max="2" width="13.08984375" customWidth="1"/>
-    <col min="3" max="3" width="17.6328125" customWidth="1"/>
-    <col min="4" max="4" width="9.81640625" customWidth="1"/>
-    <col min="5" max="5" width="10.453125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C1" t="s">
-        <v>353</v>
-      </c>
-      <c r="D1" t="s">
-        <v>273</v>
-      </c>
-      <c r="E1" t="s">
-        <v>891</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>1128</v>
-      </c>
-      <c r="B2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C2" t="s">
-        <v>310</v>
-      </c>
-      <c r="D2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E2" t="s">
-        <v>1125</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>1127</v>
-      </c>
-      <c r="B3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C3" t="s">
-        <v>310</v>
-      </c>
-      <c r="D3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E3" t="s">
-        <v>1125</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>1126</v>
-      </c>
-      <c r="B4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4" t="s">
-        <v>310</v>
-      </c>
-      <c r="D4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" t="s">
-        <v>1125</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>1124</v>
-      </c>
-      <c r="B5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C5" t="s">
-        <v>310</v>
-      </c>
-      <c r="D5" t="s">
-        <v>26</v>
-      </c>
-      <c r="E5" t="s">
-        <v>1121</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>1123</v>
-      </c>
-      <c r="B6" t="s">
-        <v>467</v>
-      </c>
-      <c r="C6" t="s">
-        <v>310</v>
-      </c>
-      <c r="D6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6" t="s">
-        <v>1121</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>1122</v>
-      </c>
-      <c r="B7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" t="s">
-        <v>310</v>
-      </c>
-      <c r="D7" t="s">
-        <v>26</v>
-      </c>
-      <c r="E7" t="s">
-        <v>1121</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>1120</v>
-      </c>
-      <c r="B8" t="s">
-        <v>30</v>
-      </c>
-      <c r="C8" t="s">
-        <v>310</v>
-      </c>
-      <c r="D8" t="s">
-        <v>26</v>
-      </c>
-      <c r="E8" t="s">
-        <v>1106</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>1119</v>
-      </c>
-      <c r="B9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C9" t="s">
-        <v>310</v>
-      </c>
-      <c r="D9" t="s">
-        <v>26</v>
-      </c>
-      <c r="E9" t="s">
-        <v>1106</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>1118</v>
-      </c>
-      <c r="B10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10" t="s">
-        <v>310</v>
-      </c>
-      <c r="D10" t="s">
-        <v>26</v>
-      </c>
-      <c r="E10" t="s">
-        <v>1106</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>1117</v>
-      </c>
-      <c r="B11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" t="s">
-        <v>310</v>
-      </c>
-      <c r="D11" t="s">
-        <v>26</v>
-      </c>
-      <c r="E11" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>1116</v>
-      </c>
-      <c r="B12" t="s">
-        <v>467</v>
-      </c>
-      <c r="C12" t="s">
-        <v>310</v>
-      </c>
-      <c r="D12" t="s">
-        <v>26</v>
-      </c>
-      <c r="E12" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>1115</v>
-      </c>
-      <c r="B13" t="s">
-        <v>27</v>
-      </c>
-      <c r="C13" t="s">
-        <v>310</v>
-      </c>
-      <c r="D13" t="s">
-        <v>26</v>
-      </c>
-      <c r="E13" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>1114</v>
-      </c>
-      <c r="B14" t="s">
-        <v>30</v>
-      </c>
-      <c r="C14" t="s">
-        <v>310</v>
-      </c>
-      <c r="D14" t="s">
-        <v>26</v>
-      </c>
-      <c r="E14" t="s">
-        <v>1111</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>1113</v>
-      </c>
-      <c r="B15" t="s">
-        <v>29</v>
-      </c>
-      <c r="C15" t="s">
-        <v>310</v>
-      </c>
-      <c r="D15" t="s">
-        <v>26</v>
-      </c>
-      <c r="E15" t="s">
-        <v>1111</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>1112</v>
-      </c>
-      <c r="B16" t="s">
-        <v>27</v>
-      </c>
-      <c r="C16" t="s">
-        <v>310</v>
-      </c>
-      <c r="D16" t="s">
-        <v>26</v>
-      </c>
-      <c r="E16" t="s">
-        <v>1111</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>1110</v>
-      </c>
-      <c r="B17" t="s">
-        <v>30</v>
-      </c>
-      <c r="C17" t="s">
-        <v>310</v>
-      </c>
-      <c r="D17" t="s">
-        <v>26</v>
-      </c>
-      <c r="E17" t="s">
-        <v>1107</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>1109</v>
-      </c>
-      <c r="B18" t="s">
-        <v>467</v>
-      </c>
-      <c r="C18" t="s">
-        <v>310</v>
-      </c>
-      <c r="D18" t="s">
-        <v>26</v>
-      </c>
-      <c r="E18" t="s">
-        <v>1107</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>1108</v>
-      </c>
-      <c r="B19" t="s">
-        <v>27</v>
-      </c>
-      <c r="C19" t="s">
-        <v>310</v>
-      </c>
-      <c r="D19" t="s">
-        <v>26</v>
-      </c>
-      <c r="E19" t="s">
-        <v>1107</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A20" s="25" t="s">
-        <v>1129</v>
-      </c>
-      <c r="B20" s="25" t="s">
-        <v>30</v>
-      </c>
-      <c r="C20" s="25" t="s">
-        <v>304</v>
-      </c>
-      <c r="D20" s="25" t="s">
-        <v>26</v>
-      </c>
-      <c r="E20" s="25" t="s">
-        <v>1125</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A21" s="25" t="s">
-        <v>1130</v>
-      </c>
-      <c r="B21" s="25" t="s">
-        <v>29</v>
-      </c>
-      <c r="C21" s="25" t="s">
-        <v>304</v>
-      </c>
-      <c r="D21" s="25" t="s">
-        <v>26</v>
-      </c>
-      <c r="E21" s="25" t="s">
-        <v>1125</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A22" s="25" t="s">
-        <v>1131</v>
-      </c>
-      <c r="B22" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="C22" s="25" t="s">
-        <v>304</v>
-      </c>
-      <c r="D22" s="25" t="s">
-        <v>26</v>
-      </c>
-      <c r="E22" s="25" t="s">
-        <v>1125</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A23" s="25" t="s">
-        <v>1132</v>
-      </c>
-      <c r="B23" s="25" t="s">
-        <v>30</v>
-      </c>
-      <c r="C23" s="25" t="s">
-        <v>304</v>
-      </c>
-      <c r="D23" s="25" t="s">
-        <v>26</v>
-      </c>
-      <c r="E23" s="25" t="s">
-        <v>1121</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A24" s="25" t="s">
-        <v>1133</v>
-      </c>
-      <c r="B24" s="25" t="s">
-        <v>467</v>
-      </c>
-      <c r="C24" s="25" t="s">
-        <v>304</v>
-      </c>
-      <c r="D24" s="25" t="s">
-        <v>26</v>
-      </c>
-      <c r="E24" s="25" t="s">
-        <v>1121</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A25" s="25" t="s">
-        <v>1134</v>
-      </c>
-      <c r="B25" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="C25" s="25" t="s">
-        <v>304</v>
-      </c>
-      <c r="D25" s="25" t="s">
-        <v>26</v>
-      </c>
-      <c r="E25" s="25" t="s">
-        <v>1121</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
-        <v>1135</v>
-      </c>
-      <c r="B26" t="s">
-        <v>30</v>
-      </c>
-      <c r="C26" t="s">
-        <v>304</v>
-      </c>
-      <c r="D26" t="s">
-        <v>26</v>
-      </c>
-      <c r="E26" t="s">
-        <v>1106</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
-        <v>1136</v>
-      </c>
-      <c r="B27" t="s">
-        <v>29</v>
-      </c>
-      <c r="C27" t="s">
-        <v>304</v>
-      </c>
-      <c r="D27" t="s">
-        <v>26</v>
-      </c>
-      <c r="E27" t="s">
-        <v>1106</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
-        <v>1137</v>
-      </c>
-      <c r="B28" t="s">
-        <v>27</v>
-      </c>
-      <c r="C28" t="s">
-        <v>304</v>
-      </c>
-      <c r="D28" t="s">
-        <v>26</v>
-      </c>
-      <c r="E28" t="s">
-        <v>1106</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
-        <v>1138</v>
-      </c>
-      <c r="B29" t="s">
-        <v>30</v>
-      </c>
-      <c r="C29" t="s">
-        <v>304</v>
-      </c>
-      <c r="D29" t="s">
-        <v>26</v>
-      </c>
-      <c r="E29" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
-        <v>1139</v>
-      </c>
-      <c r="B30" t="s">
-        <v>467</v>
-      </c>
-      <c r="C30" t="s">
-        <v>304</v>
-      </c>
-      <c r="D30" t="s">
-        <v>26</v>
-      </c>
-      <c r="E30" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
-        <v>1140</v>
-      </c>
-      <c r="B31" t="s">
-        <v>27</v>
-      </c>
-      <c r="C31" t="s">
-        <v>304</v>
-      </c>
-      <c r="D31" t="s">
-        <v>26</v>
-      </c>
-      <c r="E31" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
-        <v>1141</v>
-      </c>
-      <c r="B32" t="s">
-        <v>30</v>
-      </c>
-      <c r="C32" t="s">
-        <v>304</v>
-      </c>
-      <c r="D32" t="s">
-        <v>26</v>
-      </c>
-      <c r="E32" t="s">
-        <v>1111</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
-        <v>1142</v>
-      </c>
-      <c r="B33" t="s">
-        <v>29</v>
-      </c>
-      <c r="C33" t="s">
-        <v>304</v>
-      </c>
-      <c r="D33" t="s">
-        <v>26</v>
-      </c>
-      <c r="E33" t="s">
-        <v>1111</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A34" t="s">
-        <v>1143</v>
-      </c>
-      <c r="B34" t="s">
-        <v>27</v>
-      </c>
-      <c r="C34" t="s">
-        <v>304</v>
-      </c>
-      <c r="D34" t="s">
-        <v>26</v>
-      </c>
-      <c r="E34" t="s">
-        <v>1111</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
-        <v>1144</v>
-      </c>
-      <c r="B35" t="s">
-        <v>30</v>
-      </c>
-      <c r="C35" t="s">
-        <v>304</v>
-      </c>
-      <c r="D35" t="s">
-        <v>26</v>
-      </c>
-      <c r="E35" t="s">
-        <v>1107</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A36" t="s">
-        <v>1145</v>
-      </c>
-      <c r="B36" t="s">
-        <v>467</v>
-      </c>
-      <c r="C36" t="s">
-        <v>304</v>
-      </c>
-      <c r="D36" t="s">
-        <v>26</v>
-      </c>
-      <c r="E36" t="s">
-        <v>1107</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A37" t="s">
-        <v>1146</v>
-      </c>
-      <c r="B37" t="s">
-        <v>27</v>
-      </c>
-      <c r="C37" t="s">
-        <v>304</v>
-      </c>
-      <c r="D37" t="s">
-        <v>26</v>
-      </c>
-      <c r="E37" t="s">
-        <v>1107</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4692B37E-0216-4972-A110-E1B81B06E6C4}">
   <sheetPr codeName="Sheet3">
     <tabColor rgb="FF92D050"/>
@@ -8837,7 +8776,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED88715B-2C1F-4B02-9C56-197D358D7FB4}">
   <sheetPr codeName="Sheet4">
     <tabColor rgb="FF92D050"/>
@@ -9816,7 +9755,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F6A7684-571C-4EED-95D8-7F34A7B49B6B}">
   <sheetPr codeName="Sheet5">
     <tabColor rgb="FF92D050"/>
@@ -10104,7 +10043,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6188AC2A-13AA-44F7-B850-44BEE776D85D}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -10334,7 +10273,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01F4AAFC-C1A9-47B3-B848-06156D11375D}">
   <sheetPr codeName="Sheet6">
     <tabColor rgb="FF92D050"/>
@@ -10482,7 +10421,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63EE12FB-03D5-4E75-92F5-3C993AAF3A5A}">
   <sheetPr codeName="Sheet7">
     <tabColor rgb="FF92D050"/>
@@ -10602,7 +10541,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13C6162D-ED52-4421-8B7E-2C58681ADE6F}">
   <sheetPr codeName="Sheet8">
     <tabColor rgb="FF92D050"/>
@@ -10746,7 +10685,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{208BBAD8-8992-4A11-B32C-5E8E74095072}">
   <sheetPr codeName="Sheet9">
     <tabColor rgb="FF92D050"/>
@@ -12873,7 +12812,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{700E1104-0B81-46DF-BF55-20A13EF92D67}">
   <sheetPr codeName="Sheet11">
     <tabColor theme="5"/>
@@ -13004,7 +12943,653 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C2E8DB6-985C-4A4D-B54D-754B4AB198CD}">
+  <dimension ref="A1:E37"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="146.90625" customWidth="1"/>
+    <col min="2" max="2" width="13.08984375" customWidth="1"/>
+    <col min="3" max="3" width="17.6328125" customWidth="1"/>
+    <col min="4" max="4" width="9.81640625" customWidth="1"/>
+    <col min="5" max="5" width="10.453125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" t="s">
+        <v>353</v>
+      </c>
+      <c r="D1" t="s">
+        <v>273</v>
+      </c>
+      <c r="E1" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>1128</v>
+      </c>
+      <c r="B2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" t="s">
+        <v>310</v>
+      </c>
+      <c r="D2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" t="s">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>1127</v>
+      </c>
+      <c r="B3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3" t="s">
+        <v>310</v>
+      </c>
+      <c r="D3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" t="s">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>1126</v>
+      </c>
+      <c r="B4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" t="s">
+        <v>310</v>
+      </c>
+      <c r="D4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" t="s">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>1124</v>
+      </c>
+      <c r="B5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" t="s">
+        <v>310</v>
+      </c>
+      <c r="D5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" t="s">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>1123</v>
+      </c>
+      <c r="B6" t="s">
+        <v>467</v>
+      </c>
+      <c r="C6" t="s">
+        <v>310</v>
+      </c>
+      <c r="D6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" t="s">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>1122</v>
+      </c>
+      <c r="B7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" t="s">
+        <v>310</v>
+      </c>
+      <c r="D7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" t="s">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>1120</v>
+      </c>
+      <c r="B8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" t="s">
+        <v>310</v>
+      </c>
+      <c r="D8" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" t="s">
+        <v>1106</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" t="s">
+        <v>310</v>
+      </c>
+      <c r="D9" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" t="s">
+        <v>1106</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>1118</v>
+      </c>
+      <c r="B10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" t="s">
+        <v>310</v>
+      </c>
+      <c r="D10" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" t="s">
+        <v>1106</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>1117</v>
+      </c>
+      <c r="B11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" t="s">
+        <v>310</v>
+      </c>
+      <c r="D11" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>1116</v>
+      </c>
+      <c r="B12" t="s">
+        <v>467</v>
+      </c>
+      <c r="C12" t="s">
+        <v>310</v>
+      </c>
+      <c r="D12" t="s">
+        <v>26</v>
+      </c>
+      <c r="E12" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>1115</v>
+      </c>
+      <c r="B13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" t="s">
+        <v>310</v>
+      </c>
+      <c r="D13" t="s">
+        <v>26</v>
+      </c>
+      <c r="E13" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>1114</v>
+      </c>
+      <c r="B14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" t="s">
+        <v>310</v>
+      </c>
+      <c r="D14" t="s">
+        <v>26</v>
+      </c>
+      <c r="E14" t="s">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B15" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" t="s">
+        <v>310</v>
+      </c>
+      <c r="D15" t="s">
+        <v>26</v>
+      </c>
+      <c r="E15" t="s">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B16" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" t="s">
+        <v>310</v>
+      </c>
+      <c r="D16" t="s">
+        <v>26</v>
+      </c>
+      <c r="E16" t="s">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>1110</v>
+      </c>
+      <c r="B17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" t="s">
+        <v>310</v>
+      </c>
+      <c r="D17" t="s">
+        <v>26</v>
+      </c>
+      <c r="E17" t="s">
+        <v>1107</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>1109</v>
+      </c>
+      <c r="B18" t="s">
+        <v>467</v>
+      </c>
+      <c r="C18" t="s">
+        <v>310</v>
+      </c>
+      <c r="D18" t="s">
+        <v>26</v>
+      </c>
+      <c r="E18" t="s">
+        <v>1107</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>1108</v>
+      </c>
+      <c r="B19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" t="s">
+        <v>310</v>
+      </c>
+      <c r="D19" t="s">
+        <v>26</v>
+      </c>
+      <c r="E19" t="s">
+        <v>1107</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20" s="25" t="s">
+        <v>1129</v>
+      </c>
+      <c r="B20" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="25" t="s">
+        <v>304</v>
+      </c>
+      <c r="D20" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="E20" s="25" t="s">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21" s="25" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B21" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="C21" s="25" t="s">
+        <v>304</v>
+      </c>
+      <c r="D21" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="E21" s="25" t="s">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A22" s="25" t="s">
+        <v>1131</v>
+      </c>
+      <c r="B22" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" s="25" t="s">
+        <v>304</v>
+      </c>
+      <c r="D22" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="E22" s="25" t="s">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A23" s="25" t="s">
+        <v>1132</v>
+      </c>
+      <c r="B23" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" s="25" t="s">
+        <v>304</v>
+      </c>
+      <c r="D23" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="E23" s="25" t="s">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A24" s="25" t="s">
+        <v>1133</v>
+      </c>
+      <c r="B24" s="25" t="s">
+        <v>467</v>
+      </c>
+      <c r="C24" s="25" t="s">
+        <v>304</v>
+      </c>
+      <c r="D24" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="E24" s="25" t="s">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A25" s="25" t="s">
+        <v>1134</v>
+      </c>
+      <c r="B25" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="C25" s="25" t="s">
+        <v>304</v>
+      </c>
+      <c r="D25" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="E25" s="25" t="s">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>1135</v>
+      </c>
+      <c r="B26" t="s">
+        <v>30</v>
+      </c>
+      <c r="C26" t="s">
+        <v>304</v>
+      </c>
+      <c r="D26" t="s">
+        <v>26</v>
+      </c>
+      <c r="E26" t="s">
+        <v>1106</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>1136</v>
+      </c>
+      <c r="B27" t="s">
+        <v>29</v>
+      </c>
+      <c r="C27" t="s">
+        <v>304</v>
+      </c>
+      <c r="D27" t="s">
+        <v>26</v>
+      </c>
+      <c r="E27" t="s">
+        <v>1106</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B28" t="s">
+        <v>27</v>
+      </c>
+      <c r="C28" t="s">
+        <v>304</v>
+      </c>
+      <c r="D28" t="s">
+        <v>26</v>
+      </c>
+      <c r="E28" t="s">
+        <v>1106</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>1138</v>
+      </c>
+      <c r="B29" t="s">
+        <v>30</v>
+      </c>
+      <c r="C29" t="s">
+        <v>304</v>
+      </c>
+      <c r="D29" t="s">
+        <v>26</v>
+      </c>
+      <c r="E29" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>1139</v>
+      </c>
+      <c r="B30" t="s">
+        <v>467</v>
+      </c>
+      <c r="C30" t="s">
+        <v>304</v>
+      </c>
+      <c r="D30" t="s">
+        <v>26</v>
+      </c>
+      <c r="E30" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>1140</v>
+      </c>
+      <c r="B31" t="s">
+        <v>27</v>
+      </c>
+      <c r="C31" t="s">
+        <v>304</v>
+      </c>
+      <c r="D31" t="s">
+        <v>26</v>
+      </c>
+      <c r="E31" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B32" t="s">
+        <v>30</v>
+      </c>
+      <c r="C32" t="s">
+        <v>304</v>
+      </c>
+      <c r="D32" t="s">
+        <v>26</v>
+      </c>
+      <c r="E32" t="s">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>1142</v>
+      </c>
+      <c r="B33" t="s">
+        <v>29</v>
+      </c>
+      <c r="C33" t="s">
+        <v>304</v>
+      </c>
+      <c r="D33" t="s">
+        <v>26</v>
+      </c>
+      <c r="E33" t="s">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B34" t="s">
+        <v>27</v>
+      </c>
+      <c r="C34" t="s">
+        <v>304</v>
+      </c>
+      <c r="D34" t="s">
+        <v>26</v>
+      </c>
+      <c r="E34" t="s">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B35" t="s">
+        <v>30</v>
+      </c>
+      <c r="C35" t="s">
+        <v>304</v>
+      </c>
+      <c r="D35" t="s">
+        <v>26</v>
+      </c>
+      <c r="E35" t="s">
+        <v>1107</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>1145</v>
+      </c>
+      <c r="B36" t="s">
+        <v>467</v>
+      </c>
+      <c r="C36" t="s">
+        <v>304</v>
+      </c>
+      <c r="D36" t="s">
+        <v>26</v>
+      </c>
+      <c r="E36" t="s">
+        <v>1107</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>1146</v>
+      </c>
+      <c r="B37" t="s">
+        <v>27</v>
+      </c>
+      <c r="C37" t="s">
+        <v>304</v>
+      </c>
+      <c r="D37" t="s">
+        <v>26</v>
+      </c>
+      <c r="E37" t="s">
+        <v>1107</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{604C20EA-1202-4F32-9A03-50C03C9141BD}">
   <sheetPr codeName="Sheet12">
     <tabColor theme="5"/>
@@ -13105,182 +13690,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB0C9BC5-E2CE-4417-A398-52D4FBA952C1}">
-  <dimension ref="A1:M11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="10.90625" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" customWidth="1"/>
-    <col min="13" max="13" width="86.6328125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>353</v>
-      </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
-        <v>302</v>
-      </c>
-      <c r="D1" t="s">
-        <v>65</v>
-      </c>
-      <c r="E1" t="s">
-        <v>147</v>
-      </c>
-      <c r="F1" t="s">
-        <v>187</v>
-      </c>
-      <c r="G1" t="s">
-        <v>179</v>
-      </c>
-      <c r="H1" t="s">
-        <v>180</v>
-      </c>
-      <c r="I1" t="s">
-        <v>1057</v>
-      </c>
-      <c r="J1" t="s">
-        <v>89</v>
-      </c>
-      <c r="K1" t="s">
-        <v>273</v>
-      </c>
-      <c r="L1" t="s">
-        <v>1058</v>
-      </c>
-      <c r="M1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>1059</v>
-      </c>
-      <c r="M2" t="s">
-        <v>1060</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>1061</v>
-      </c>
-      <c r="B3" t="s">
-        <v>540</v>
-      </c>
-      <c r="M3" t="s">
-        <v>1062</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>1063</v>
-      </c>
-      <c r="M4" t="s">
-        <v>1064</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>1065</v>
-      </c>
-      <c r="M5" t="s">
-        <v>1066</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>1067</v>
-      </c>
-      <c r="M6" t="s">
-        <v>1068</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>1069</v>
-      </c>
-      <c r="M7" t="s">
-        <v>1070</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>1071</v>
-      </c>
-      <c r="B8" t="s">
-        <v>326</v>
-      </c>
-      <c r="M8" t="s">
-        <v>1072</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>1073</v>
-      </c>
-      <c r="M9" t="s">
-        <v>1074</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>1075</v>
-      </c>
-      <c r="B10" t="s">
-        <v>326</v>
-      </c>
-      <c r="M10" t="s">
-        <v>1076</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>49</v>
-      </c>
-      <c r="C11" t="s">
-        <v>12</v>
-      </c>
-      <c r="D11" t="s">
-        <v>30</v>
-      </c>
-      <c r="E11" t="s">
-        <v>15</v>
-      </c>
-      <c r="F11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G11" t="s">
-        <v>181</v>
-      </c>
-      <c r="H11">
-        <v>2</v>
-      </c>
-      <c r="I11" t="s">
-        <v>208</v>
-      </c>
-      <c r="J11" t="s">
-        <v>91</v>
-      </c>
-      <c r="K11" t="s">
-        <v>26</v>
-      </c>
-      <c r="L11" t="s">
-        <v>100</v>
-      </c>
-      <c r="M11" t="s">
-        <v>1077</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6364318-D354-4A54-B885-C4D13BCF1553}">
   <sheetPr codeName="Sheet13">
     <tabColor theme="5"/>
@@ -13484,7 +13894,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86AB462C-E7DD-41D5-B1F6-0B76A79BD546}">
   <sheetPr codeName="Sheet10">
     <tabColor theme="5"/>
@@ -13618,7 +14028,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0DA0612-5B2C-41D1-B114-8D7F9449CFCB}">
   <sheetPr>
     <tabColor theme="5"/>
@@ -13804,7 +14214,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF4B8566-925A-4EBE-8FA2-F566554280EF}">
   <sheetPr codeName="Sheet14">
     <tabColor theme="5"/>
@@ -14195,7 +14605,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8162057B-52FF-4F06-A9FE-C8E0168242E3}">
   <sheetPr codeName="Sheet15">
     <tabColor rgb="FF92D050"/>
@@ -14336,7 +14746,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32DCD494-48E9-4641-90F2-206CAB2F7041}">
   <sheetPr codeName="Sheet16">
     <tabColor rgb="FF92D050"/>
@@ -14561,7 +14971,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D72A9D9-D447-4A21-A49D-88C8132B73CE}">
   <sheetPr codeName="Sheet17">
     <tabColor theme="5"/>
@@ -14760,7 +15170,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05F5A9AB-486E-4615-848C-03E69B3477F9}">
   <sheetPr codeName="Sheet18">
     <tabColor theme="5"/>
@@ -14968,7 +15378,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{699F63E1-0070-48F6-AF52-8BCBFD9B07EF}">
   <sheetPr codeName="Sheet19">
     <tabColor theme="5"/>
@@ -15127,7 +15537,182 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB0C9BC5-E2CE-4417-A398-52D4FBA952C1}">
+  <dimension ref="A1:M11"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="10.90625" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" customWidth="1"/>
+    <col min="13" max="13" width="86.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>353</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>302</v>
+      </c>
+      <c r="D1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E1" t="s">
+        <v>147</v>
+      </c>
+      <c r="F1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G1" t="s">
+        <v>179</v>
+      </c>
+      <c r="H1" t="s">
+        <v>180</v>
+      </c>
+      <c r="I1" t="s">
+        <v>1057</v>
+      </c>
+      <c r="J1" t="s">
+        <v>89</v>
+      </c>
+      <c r="K1" t="s">
+        <v>273</v>
+      </c>
+      <c r="L1" t="s">
+        <v>1058</v>
+      </c>
+      <c r="M1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>1059</v>
+      </c>
+      <c r="M2" t="s">
+        <v>1060</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>1061</v>
+      </c>
+      <c r="B3" t="s">
+        <v>540</v>
+      </c>
+      <c r="M3" t="s">
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="M4" t="s">
+        <v>1064</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>1065</v>
+      </c>
+      <c r="M5" t="s">
+        <v>1066</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>1067</v>
+      </c>
+      <c r="M6" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>1069</v>
+      </c>
+      <c r="M7" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B8" t="s">
+        <v>326</v>
+      </c>
+      <c r="M8" t="s">
+        <v>1072</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>1073</v>
+      </c>
+      <c r="M9" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B10" t="s">
+        <v>326</v>
+      </c>
+      <c r="M10" t="s">
+        <v>1076</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>49</v>
+      </c>
+      <c r="C11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" t="s">
+        <v>30</v>
+      </c>
+      <c r="E11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" t="s">
+        <v>181</v>
+      </c>
+      <c r="H11">
+        <v>2</v>
+      </c>
+      <c r="I11" t="s">
+        <v>208</v>
+      </c>
+      <c r="J11" t="s">
+        <v>91</v>
+      </c>
+      <c r="K11" t="s">
+        <v>26</v>
+      </c>
+      <c r="L11" t="s">
+        <v>100</v>
+      </c>
+      <c r="M11" t="s">
+        <v>1077</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{783D1FEC-B865-44FA-820C-57E3FB6789F2}">
   <sheetPr codeName="Sheet20"/>
   <dimension ref="A1:B7"/>
@@ -15201,7 +15786,525 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81503B49-E101-4423-8FFF-B866835D92EC}">
+  <sheetPr codeName="Sheet21"/>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="30.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.453125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CCEF9F3-3285-454F-A311-2FAE775A4BE5}">
+  <sheetPr codeName="Sheet22">
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
+  <dimension ref="A1:G19"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="47.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.1796875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F1" t="s">
+        <v>279</v>
+      </c>
+      <c r="G1" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F2" t="s">
+        <v>326</v>
+      </c>
+      <c r="G2" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F3" t="s">
+        <v>326</v>
+      </c>
+      <c r="G3" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E4" t="s">
+        <v>81</v>
+      </c>
+      <c r="F4" t="s">
+        <v>326</v>
+      </c>
+      <c r="G4" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D5" t="s">
+        <v>79</v>
+      </c>
+      <c r="E5" t="s">
+        <v>80</v>
+      </c>
+      <c r="F5" t="s">
+        <v>326</v>
+      </c>
+      <c r="G5" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>246</v>
+      </c>
+      <c r="B6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D6" t="s">
+        <v>79</v>
+      </c>
+      <c r="E6" t="s">
+        <v>80</v>
+      </c>
+      <c r="F6" t="s">
+        <v>326</v>
+      </c>
+      <c r="G6" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>274</v>
+      </c>
+      <c r="B7" t="s">
+        <v>275</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>272</v>
+      </c>
+      <c r="E7" t="s">
+        <v>273</v>
+      </c>
+      <c r="F7" t="s">
+        <v>326</v>
+      </c>
+      <c r="G7" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>276</v>
+      </c>
+      <c r="B8" t="s">
+        <v>275</v>
+      </c>
+      <c r="C8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" t="s">
+        <v>272</v>
+      </c>
+      <c r="E8" t="s">
+        <v>273</v>
+      </c>
+      <c r="F8" t="s">
+        <v>326</v>
+      </c>
+      <c r="G8" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>277</v>
+      </c>
+      <c r="B9" t="s">
+        <v>275</v>
+      </c>
+      <c r="C9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D9" t="s">
+        <v>272</v>
+      </c>
+      <c r="E9" t="s">
+        <v>273</v>
+      </c>
+      <c r="F9" t="s">
+        <v>326</v>
+      </c>
+      <c r="G9" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>278</v>
+      </c>
+      <c r="B10" t="s">
+        <v>275</v>
+      </c>
+      <c r="C10" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" t="s">
+        <v>272</v>
+      </c>
+      <c r="E10" t="s">
+        <v>273</v>
+      </c>
+      <c r="F10" t="s">
+        <v>326</v>
+      </c>
+      <c r="G10" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>69</v>
+      </c>
+      <c r="B11" t="s">
+        <v>70</v>
+      </c>
+      <c r="C11" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" t="s">
+        <v>78</v>
+      </c>
+      <c r="E11" t="s">
+        <v>81</v>
+      </c>
+      <c r="F11" t="s">
+        <v>326</v>
+      </c>
+      <c r="G11" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>290</v>
+      </c>
+      <c r="B12" t="s">
+        <v>70</v>
+      </c>
+      <c r="C12" t="s">
+        <v>72</v>
+      </c>
+      <c r="D12" t="s">
+        <v>78</v>
+      </c>
+      <c r="E12" t="s">
+        <v>81</v>
+      </c>
+      <c r="F12" t="s">
+        <v>326</v>
+      </c>
+      <c r="G12" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>291</v>
+      </c>
+      <c r="B13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C13" t="s">
+        <v>73</v>
+      </c>
+      <c r="D13" t="s">
+        <v>78</v>
+      </c>
+      <c r="E13" t="s">
+        <v>81</v>
+      </c>
+      <c r="F13" t="s">
+        <v>326</v>
+      </c>
+      <c r="G13" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>292</v>
+      </c>
+      <c r="B14" t="s">
+        <v>76</v>
+      </c>
+      <c r="C14" t="s">
+        <v>64</v>
+      </c>
+      <c r="D14" t="s">
+        <v>79</v>
+      </c>
+      <c r="E14" t="s">
+        <v>80</v>
+      </c>
+      <c r="F14" t="s">
+        <v>326</v>
+      </c>
+      <c r="G14" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>293</v>
+      </c>
+      <c r="B15" t="s">
+        <v>76</v>
+      </c>
+      <c r="C15" t="s">
+        <v>146</v>
+      </c>
+      <c r="D15" t="s">
+        <v>79</v>
+      </c>
+      <c r="E15" t="s">
+        <v>80</v>
+      </c>
+      <c r="F15" t="s">
+        <v>326</v>
+      </c>
+      <c r="G15" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>294</v>
+      </c>
+      <c r="B16" t="s">
+        <v>275</v>
+      </c>
+      <c r="C16" t="s">
+        <v>26</v>
+      </c>
+      <c r="D16" t="s">
+        <v>272</v>
+      </c>
+      <c r="E16" t="s">
+        <v>273</v>
+      </c>
+      <c r="F16" t="s">
+        <v>326</v>
+      </c>
+      <c r="G16" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>295</v>
+      </c>
+      <c r="B17" t="s">
+        <v>275</v>
+      </c>
+      <c r="C17" t="s">
+        <v>25</v>
+      </c>
+      <c r="D17" t="s">
+        <v>272</v>
+      </c>
+      <c r="E17" t="s">
+        <v>273</v>
+      </c>
+      <c r="F17" t="s">
+        <v>326</v>
+      </c>
+      <c r="G17" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>296</v>
+      </c>
+      <c r="B18" t="s">
+        <v>275</v>
+      </c>
+      <c r="C18" t="s">
+        <v>43</v>
+      </c>
+      <c r="D18" t="s">
+        <v>272</v>
+      </c>
+      <c r="E18" t="s">
+        <v>273</v>
+      </c>
+      <c r="F18" t="s">
+        <v>326</v>
+      </c>
+      <c r="G18" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>297</v>
+      </c>
+      <c r="B19" t="s">
+        <v>275</v>
+      </c>
+      <c r="C19" t="s">
+        <v>23</v>
+      </c>
+      <c r="D19" t="s">
+        <v>272</v>
+      </c>
+      <c r="E19" t="s">
+        <v>273</v>
+      </c>
+      <c r="F19" t="s">
+        <v>326</v>
+      </c>
+      <c r="G19" t="s">
+        <v>289</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A1" location="Index!A1" display="TestCaseName" xr:uid="{17A34A3D-FCB4-496D-83D9-9CD80D0ED2D3}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{228A5EA1-7578-437E-943F-B5DA9932AB71}">
   <dimension ref="A1:H13"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -15524,525 +16627,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81503B49-E101-4423-8FFF-B866835D92EC}">
-  <sheetPr codeName="Sheet21"/>
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="30.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.453125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>54</v>
-      </c>
-      <c r="B4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>55</v>
-      </c>
-      <c r="B5" t="s">
-        <v>24</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CCEF9F3-3285-454F-A311-2FAE775A4BE5}">
-  <sheetPr codeName="Sheet22">
-    <tabColor rgb="FF92D050"/>
-  </sheetPr>
-  <dimension ref="A1:G19"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="47.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.1796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.36328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.1796875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A1" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C1" t="s">
-        <v>63</v>
-      </c>
-      <c r="D1" t="s">
-        <v>62</v>
-      </c>
-      <c r="E1" t="s">
-        <v>82</v>
-      </c>
-      <c r="F1" t="s">
-        <v>279</v>
-      </c>
-      <c r="G1" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" t="s">
-        <v>78</v>
-      </c>
-      <c r="E2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F2" t="s">
-        <v>326</v>
-      </c>
-      <c r="G2" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>71</v>
-      </c>
-      <c r="B3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D3" t="s">
-        <v>78</v>
-      </c>
-      <c r="E3" t="s">
-        <v>81</v>
-      </c>
-      <c r="F3" t="s">
-        <v>326</v>
-      </c>
-      <c r="G3" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>74</v>
-      </c>
-      <c r="B4" t="s">
-        <v>70</v>
-      </c>
-      <c r="C4" t="s">
-        <v>73</v>
-      </c>
-      <c r="D4" t="s">
-        <v>78</v>
-      </c>
-      <c r="E4" t="s">
-        <v>81</v>
-      </c>
-      <c r="F4" t="s">
-        <v>326</v>
-      </c>
-      <c r="G4" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>75</v>
-      </c>
-      <c r="B5" t="s">
-        <v>76</v>
-      </c>
-      <c r="C5" t="s">
-        <v>64</v>
-      </c>
-      <c r="D5" t="s">
-        <v>79</v>
-      </c>
-      <c r="E5" t="s">
-        <v>80</v>
-      </c>
-      <c r="F5" t="s">
-        <v>326</v>
-      </c>
-      <c r="G5" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>246</v>
-      </c>
-      <c r="B6" t="s">
-        <v>76</v>
-      </c>
-      <c r="C6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D6" t="s">
-        <v>79</v>
-      </c>
-      <c r="E6" t="s">
-        <v>80</v>
-      </c>
-      <c r="F6" t="s">
-        <v>326</v>
-      </c>
-      <c r="G6" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>274</v>
-      </c>
-      <c r="B7" t="s">
-        <v>275</v>
-      </c>
-      <c r="C7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" t="s">
-        <v>272</v>
-      </c>
-      <c r="E7" t="s">
-        <v>273</v>
-      </c>
-      <c r="F7" t="s">
-        <v>326</v>
-      </c>
-      <c r="G7" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>276</v>
-      </c>
-      <c r="B8" t="s">
-        <v>275</v>
-      </c>
-      <c r="C8" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8" t="s">
-        <v>272</v>
-      </c>
-      <c r="E8" t="s">
-        <v>273</v>
-      </c>
-      <c r="F8" t="s">
-        <v>326</v>
-      </c>
-      <c r="G8" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>277</v>
-      </c>
-      <c r="B9" t="s">
-        <v>275</v>
-      </c>
-      <c r="C9" t="s">
-        <v>43</v>
-      </c>
-      <c r="D9" t="s">
-        <v>272</v>
-      </c>
-      <c r="E9" t="s">
-        <v>273</v>
-      </c>
-      <c r="F9" t="s">
-        <v>326</v>
-      </c>
-      <c r="G9" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>278</v>
-      </c>
-      <c r="B10" t="s">
-        <v>275</v>
-      </c>
-      <c r="C10" t="s">
-        <v>23</v>
-      </c>
-      <c r="D10" t="s">
-        <v>272</v>
-      </c>
-      <c r="E10" t="s">
-        <v>273</v>
-      </c>
-      <c r="F10" t="s">
-        <v>326</v>
-      </c>
-      <c r="G10" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>69</v>
-      </c>
-      <c r="B11" t="s">
-        <v>70</v>
-      </c>
-      <c r="C11" t="s">
-        <v>15</v>
-      </c>
-      <c r="D11" t="s">
-        <v>78</v>
-      </c>
-      <c r="E11" t="s">
-        <v>81</v>
-      </c>
-      <c r="F11" t="s">
-        <v>326</v>
-      </c>
-      <c r="G11" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>290</v>
-      </c>
-      <c r="B12" t="s">
-        <v>70</v>
-      </c>
-      <c r="C12" t="s">
-        <v>72</v>
-      </c>
-      <c r="D12" t="s">
-        <v>78</v>
-      </c>
-      <c r="E12" t="s">
-        <v>81</v>
-      </c>
-      <c r="F12" t="s">
-        <v>326</v>
-      </c>
-      <c r="G12" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>291</v>
-      </c>
-      <c r="B13" t="s">
-        <v>70</v>
-      </c>
-      <c r="C13" t="s">
-        <v>73</v>
-      </c>
-      <c r="D13" t="s">
-        <v>78</v>
-      </c>
-      <c r="E13" t="s">
-        <v>81</v>
-      </c>
-      <c r="F13" t="s">
-        <v>326</v>
-      </c>
-      <c r="G13" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>292</v>
-      </c>
-      <c r="B14" t="s">
-        <v>76</v>
-      </c>
-      <c r="C14" t="s">
-        <v>64</v>
-      </c>
-      <c r="D14" t="s">
-        <v>79</v>
-      </c>
-      <c r="E14" t="s">
-        <v>80</v>
-      </c>
-      <c r="F14" t="s">
-        <v>326</v>
-      </c>
-      <c r="G14" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>293</v>
-      </c>
-      <c r="B15" t="s">
-        <v>76</v>
-      </c>
-      <c r="C15" t="s">
-        <v>146</v>
-      </c>
-      <c r="D15" t="s">
-        <v>79</v>
-      </c>
-      <c r="E15" t="s">
-        <v>80</v>
-      </c>
-      <c r="F15" t="s">
-        <v>326</v>
-      </c>
-      <c r="G15" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>294</v>
-      </c>
-      <c r="B16" t="s">
-        <v>275</v>
-      </c>
-      <c r="C16" t="s">
-        <v>26</v>
-      </c>
-      <c r="D16" t="s">
-        <v>272</v>
-      </c>
-      <c r="E16" t="s">
-        <v>273</v>
-      </c>
-      <c r="F16" t="s">
-        <v>326</v>
-      </c>
-      <c r="G16" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>295</v>
-      </c>
-      <c r="B17" t="s">
-        <v>275</v>
-      </c>
-      <c r="C17" t="s">
-        <v>25</v>
-      </c>
-      <c r="D17" t="s">
-        <v>272</v>
-      </c>
-      <c r="E17" t="s">
-        <v>273</v>
-      </c>
-      <c r="F17" t="s">
-        <v>326</v>
-      </c>
-      <c r="G17" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>296</v>
-      </c>
-      <c r="B18" t="s">
-        <v>275</v>
-      </c>
-      <c r="C18" t="s">
-        <v>43</v>
-      </c>
-      <c r="D18" t="s">
-        <v>272</v>
-      </c>
-      <c r="E18" t="s">
-        <v>273</v>
-      </c>
-      <c r="F18" t="s">
-        <v>326</v>
-      </c>
-      <c r="G18" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>297</v>
-      </c>
-      <c r="B19" t="s">
-        <v>275</v>
-      </c>
-      <c r="C19" t="s">
-        <v>23</v>
-      </c>
-      <c r="D19" t="s">
-        <v>272</v>
-      </c>
-      <c r="E19" t="s">
-        <v>273</v>
-      </c>
-      <c r="F19" t="s">
-        <v>326</v>
-      </c>
-      <c r="G19" t="s">
-        <v>289</v>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="A1" location="Index!A1" display="TestCaseName" xr:uid="{17A34A3D-FCB4-496D-83D9-9CD80D0ED2D3}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4A529B9-903C-45A2-901F-9D341955071D}">
   <dimension ref="A1:D20"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -16341,7 +16926,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38E2CB3A-76BE-454A-8CED-01A84C1CCF2F}">
   <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -16572,7 +17157,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE3050C8-3A8D-4DE1-9C22-09145670512E}">
   <dimension ref="A1:F11"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -16813,7 +17398,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8004406F-9BB5-44CC-B5FD-6AB51EA63268}">
   <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -16885,191 +17470,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BDEB086-7FEB-4B39-87A9-1F088DACEF5D}">
-  <sheetPr>
-    <tabColor rgb="FF92D050"/>
-  </sheetPr>
-  <dimension ref="A1:D12"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="56.453125" customWidth="1"/>
-    <col min="2" max="2" width="24.08984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.54296875" customWidth="1"/>
-    <col min="4" max="4" width="14.6328125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" t="s">
-        <v>254</v>
-      </c>
-      <c r="C1" t="s">
-        <v>255</v>
-      </c>
-      <c r="D1" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>247</v>
-      </c>
-      <c r="B2" t="s">
-        <v>259</v>
-      </c>
-      <c r="C2" t="s">
-        <v>256</v>
-      </c>
-      <c r="D2" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>248</v>
-      </c>
-      <c r="B3" t="s">
-        <v>259</v>
-      </c>
-      <c r="C3" t="s">
-        <v>256</v>
-      </c>
-      <c r="D3" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>249</v>
-      </c>
-      <c r="B4" t="s">
-        <v>250</v>
-      </c>
-      <c r="C4" t="s">
-        <v>256</v>
-      </c>
-      <c r="D4" t="s">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>251</v>
-      </c>
-      <c r="B5" t="s">
-        <v>252</v>
-      </c>
-      <c r="C5" t="s">
-        <v>256</v>
-      </c>
-      <c r="D5" t="s">
-        <v>691</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>253</v>
-      </c>
-      <c r="B6" t="s">
-        <v>250</v>
-      </c>
-      <c r="C6" t="s">
-        <v>257</v>
-      </c>
-      <c r="D6" t="s">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>655</v>
-      </c>
-      <c r="C7" t="s">
-        <v>656</v>
-      </c>
-      <c r="D7" t="s">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>657</v>
-      </c>
-      <c r="B8" t="s">
-        <v>540</v>
-      </c>
-      <c r="C8" t="s">
-        <v>256</v>
-      </c>
-      <c r="D8" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>780</v>
-      </c>
-      <c r="B9" t="s">
-        <v>781</v>
-      </c>
-      <c r="C9" t="s">
-        <v>782</v>
-      </c>
-      <c r="D9" t="s">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>784</v>
-      </c>
-      <c r="B10" t="s">
-        <v>785</v>
-      </c>
-      <c r="C10" t="s">
-        <v>783</v>
-      </c>
-      <c r="D10" t="s">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>786</v>
-      </c>
-      <c r="B11" t="s">
-        <v>787</v>
-      </c>
-      <c r="C11" t="s">
-        <v>257</v>
-      </c>
-      <c r="D11" t="s">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>789</v>
-      </c>
-      <c r="B12" t="s">
-        <v>788</v>
-      </c>
-      <c r="C12" t="s">
-        <v>257</v>
-      </c>
-      <c r="D12" t="s">
-        <v>690</v>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="A1" location="Index!A1" display="TestCaseName" xr:uid="{7DBFE464-6614-48D5-A3DF-EA70153B35D9}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>